--- a/db.xlsx
+++ b/db.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DS\Petro_DB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF3E203C-320E-4517-B050-5AA7AC2855EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10F8B228-E12D-4ED3-A8F4-43EB7A97072B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15480" yWindow="-1200" windowWidth="15600" windowHeight="18720" firstSheet="6" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="material_master" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2004" uniqueCount="731">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2029" uniqueCount="736">
   <si>
     <t>remarks</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2208,9 +2208,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Diemethyl Carbonate</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2622,6 +2619,30 @@
   </si>
   <si>
     <t>여수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R087</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ethylene to 1-Hexene</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R088</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1-Butene to 1-Octene</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1-Octene</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M095</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2736,7 +2757,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2750,7 +2771,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -2998,8 +3018,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{58A5DC12-C774-4094-B2D2-06384F4F2631}" name="표2" displayName="표2" ref="A1:G95" totalsRowShown="0">
-  <autoFilter ref="A1:G95" xr:uid="{58A5DC12-C774-4094-B2D2-06384F4F2631}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{58A5DC12-C774-4094-B2D2-06384F4F2631}" name="표2" displayName="표2" ref="A1:G96" totalsRowShown="0">
+  <autoFilter ref="A1:G96" xr:uid="{58A5DC12-C774-4094-B2D2-06384F4F2631}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{8A7558A9-C918-4FAF-8C33-C287BE025DB3}" name="material_id"/>
     <tableColumn id="2" xr3:uid="{E0883773-7DC7-45AF-85B7-C29E7A5E523F}" name="material_name"/>
@@ -3014,8 +3034,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8218A6AD-F328-4A1F-A40F-562BCA5E0481}" name="표1" displayName="표1" ref="A1:E87" totalsRowShown="0">
-  <autoFilter ref="A1:E87" xr:uid="{8218A6AD-F328-4A1F-A40F-562BCA5E0481}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8218A6AD-F328-4A1F-A40F-562BCA5E0481}" name="표1" displayName="표1" ref="A1:E89" totalsRowShown="0">
+  <autoFilter ref="A1:E89" xr:uid="{8218A6AD-F328-4A1F-A40F-562BCA5E0481}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{AF938E6E-C78E-4989-A143-981F636038A6}" name="route_id"/>
     <tableColumn id="2" xr3:uid="{50E61679-5C9C-455A-95D3-37527A15BDC8}" name="route_name"/>
@@ -3028,8 +3048,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{319F947D-5803-497C-B347-524BAFE83880}" name="표3" displayName="표3" ref="A1:E99" totalsRowShown="0">
-  <autoFilter ref="A1:E99" xr:uid="{319F947D-5803-497C-B347-524BAFE83880}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{319F947D-5803-497C-B347-524BAFE83880}" name="표3" displayName="표3" ref="A1:E101" totalsRowShown="0">
+  <autoFilter ref="A1:E101" xr:uid="{319F947D-5803-497C-B347-524BAFE83880}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{37B4BF0E-EF23-494D-81CC-3F6E2B985A80}" name="route_id"/>
     <tableColumn id="2" xr3:uid="{F6F34623-0A9E-4A1B-B06B-612FA79053FF}" name="material_id"/>
@@ -3042,8 +3062,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{AE0509C7-E76F-4AAE-A013-BED08697F5A0}" name="표4" displayName="표4" ref="A1:E88" totalsRowShown="0">
-  <autoFilter ref="A1:E88" xr:uid="{AE0509C7-E76F-4AAE-A013-BED08697F5A0}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{AE0509C7-E76F-4AAE-A013-BED08697F5A0}" name="표4" displayName="표4" ref="A1:E90" totalsRowShown="0">
+  <autoFilter ref="A1:E90" xr:uid="{AE0509C7-E76F-4AAE-A013-BED08697F5A0}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{172ED76C-8FE1-403B-B64B-006301660189}" name="route_id"/>
     <tableColumn id="2" xr3:uid="{CD7417C0-560D-4558-A022-474C0791BFCE}" name="material_id"/>
@@ -3068,8 +3088,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{2680B997-BCC4-46D6-8AD7-34F304E1EBEC}" name="표5" displayName="표5" ref="A1:C57" totalsRowShown="0">
-  <autoFilter ref="A1:C57" xr:uid="{2680B997-BCC4-46D6-8AD7-34F304E1EBEC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{2680B997-BCC4-46D6-8AD7-34F304E1EBEC}" name="표5" displayName="표5" ref="A1:C59" totalsRowShown="0">
+  <autoFilter ref="A1:C59" xr:uid="{2680B997-BCC4-46D6-8AD7-34F304E1EBEC}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{D8B171A9-42A8-4A07-B62D-03279BCC372A}" name="route_id"/>
     <tableColumn id="2" xr3:uid="{0E32030E-C5E7-45E2-886D-44821472BFEA}" name="licensor_id"/>
@@ -3984,7 +4004,7 @@
         <v>3340</v>
       </c>
       <c r="F31" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
@@ -4322,7 +4342,7 @@
         <v>14</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="E50" s="1">
         <v>4230</v>
@@ -4580,7 +4600,7 @@
         <v>10</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="E64" s="1">
         <v>6250</v>
@@ -4937,15 +4957,15 @@
         <v>2370</v>
       </c>
       <c r="F83" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B84" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C84" t="s">
         <v>569</v>
@@ -4957,15 +4977,15 @@
         <v>2610</v>
       </c>
       <c r="F84" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B85" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C85" t="s">
         <v>569</v>
@@ -4977,15 +4997,15 @@
         <v>2620</v>
       </c>
       <c r="F85" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B86" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C86" t="s">
         <v>471</v>
@@ -4997,15 +5017,15 @@
         <v>6410</v>
       </c>
       <c r="F86" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B87" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C87" t="s">
         <v>503</v>
@@ -5017,15 +5037,15 @@
         <v>7100</v>
       </c>
       <c r="F87" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B88" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C88" t="s">
         <v>505</v>
@@ -5042,10 +5062,10 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B89" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="C89" t="s">
         <v>505</v>
@@ -5062,10 +5082,10 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B90" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C90" t="s">
         <v>505</v>
@@ -5082,7 +5102,7 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B91" t="s">
         <v>511</v>
@@ -5102,7 +5122,7 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B92" t="s">
         <v>512</v>
@@ -5122,7 +5142,7 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B93" t="s">
         <v>513</v>
@@ -5142,10 +5162,10 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
+        <v>689</v>
+      </c>
+      <c r="B94" t="s">
         <v>690</v>
-      </c>
-      <c r="B94" t="s">
-        <v>691</v>
       </c>
       <c r="C94" t="s">
         <v>505</v>
@@ -5157,12 +5177,12 @@
         <v>8330</v>
       </c>
       <c r="F94" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B95" t="s">
         <v>282</v>
@@ -5177,12 +5197,24 @@
         <v>3350</v>
       </c>
       <c r="F95" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="F96" s="11" t="s">
-        <v>621</v>
+      <c r="A96" t="s">
+        <v>735</v>
+      </c>
+      <c r="B96" t="s">
+        <v>734</v>
+      </c>
+      <c r="C96" t="s">
+        <v>569</v>
+      </c>
+      <c r="D96" t="s">
+        <v>509</v>
+      </c>
+      <c r="E96">
+        <v>2730</v>
       </c>
     </row>
   </sheetData>
@@ -5199,7 +5231,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD555547-6CA4-43C0-947A-5034E027DB5A}">
-  <dimension ref="A1:E87"/>
+  <dimension ref="A1:E89"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.875" bestFit="1" customWidth="1"/>
@@ -6260,13 +6292,13 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
+        <v>622</v>
+      </c>
+      <c r="B71" t="s">
         <v>623</v>
       </c>
-      <c r="B71" t="s">
+      <c r="C71" t="s">
         <v>624</v>
-      </c>
-      <c r="C71" t="s">
-        <v>625</v>
       </c>
       <c r="D71">
         <v>2</v>
@@ -6274,30 +6306,30 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
+        <v>625</v>
+      </c>
+      <c r="B72" t="s">
         <v>626</v>
       </c>
-      <c r="B72" t="s">
+      <c r="C72" t="s">
         <v>627</v>
-      </c>
-      <c r="C72" t="s">
-        <v>628</v>
       </c>
       <c r="D72">
         <v>3</v>
       </c>
       <c r="E72" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B73" t="s">
+        <v>638</v>
+      </c>
+      <c r="C73" t="s">
         <v>639</v>
-      </c>
-      <c r="C73" t="s">
-        <v>640</v>
       </c>
       <c r="D73">
         <v>2</v>
@@ -6305,61 +6337,61 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B74" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C74" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D74">
         <v>2</v>
       </c>
       <c r="E74" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
+        <v>643</v>
+      </c>
+      <c r="B75" t="s">
         <v>644</v>
       </c>
-      <c r="B75" t="s">
+      <c r="C75" t="s">
         <v>645</v>
       </c>
-      <c r="C75" t="s">
+      <c r="D75">
+        <v>1</v>
+      </c>
+      <c r="E75" t="s">
         <v>646</v>
-      </c>
-      <c r="D75">
-        <v>1</v>
-      </c>
-      <c r="E75" t="s">
-        <v>647</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
+        <v>653</v>
+      </c>
+      <c r="B76" t="s">
         <v>654</v>
       </c>
-      <c r="B76" t="s">
-        <v>655</v>
-      </c>
       <c r="C76" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D76">
         <v>2</v>
       </c>
       <c r="E76" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B77" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C77" t="s">
         <v>151</v>
@@ -6370,27 +6402,27 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B78" t="s">
+        <v>658</v>
+      </c>
+      <c r="C78" t="s">
         <v>659</v>
       </c>
-      <c r="C78" t="s">
-        <v>660</v>
-      </c>
       <c r="D78">
         <v>1</v>
       </c>
       <c r="E78" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B79" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="C79" t="s">
         <v>151</v>
@@ -6401,13 +6433,13 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B80" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="C80" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="D80">
         <v>1</v>
@@ -6415,13 +6447,13 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B81" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="C81" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="D81">
         <v>1</v>
@@ -6429,13 +6461,13 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B82" t="s">
+        <v>674</v>
+      </c>
+      <c r="C82" t="s">
         <v>675</v>
-      </c>
-      <c r="C82" t="s">
-        <v>676</v>
       </c>
       <c r="D82">
         <v>1</v>
@@ -6443,10 +6475,10 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B83" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="C83" t="s">
         <v>615</v>
@@ -6457,10 +6489,10 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B84" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C84" t="s">
         <v>615</v>
@@ -6471,10 +6503,10 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B85" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="C85" t="s">
         <v>615</v>
@@ -6485,10 +6517,10 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B86" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="C86" t="s">
         <v>615</v>
@@ -6499,19 +6531,47 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
+        <v>694</v>
+      </c>
+      <c r="B87" t="s">
+        <v>692</v>
+      </c>
+      <c r="C87" t="s">
         <v>695</v>
-      </c>
-      <c r="B87" t="s">
-        <v>693</v>
-      </c>
-      <c r="C87" t="s">
-        <v>696</v>
       </c>
       <c r="D87">
         <v>3</v>
       </c>
       <c r="E87" t="s">
-        <v>694</v>
+        <v>693</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>730</v>
+      </c>
+      <c r="B88" t="s">
+        <v>731</v>
+      </c>
+      <c r="C88" t="s">
+        <v>577</v>
+      </c>
+      <c r="D88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>732</v>
+      </c>
+      <c r="B89" t="s">
+        <v>733</v>
+      </c>
+      <c r="C89" t="s">
+        <v>577</v>
+      </c>
+      <c r="D89">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -6526,7 +6586,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDFAB716-5D9E-4323-B5B0-31948BE7F75C}">
-  <dimension ref="A1:E99"/>
+  <dimension ref="A1:E101"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.875" bestFit="1" customWidth="1"/>
@@ -7739,10 +7799,10 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B81" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C81" t="s">
         <v>609</v>
@@ -7753,7 +7813,7 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B82" t="s">
         <v>616</v>
@@ -7767,7 +7827,7 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B83" t="s">
         <v>498</v>
@@ -7781,7 +7841,7 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B84" t="s">
         <v>59</v>
@@ -7795,7 +7855,7 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B85" t="s">
         <v>59</v>
@@ -7809,7 +7869,7 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B86" t="s">
         <v>595</v>
@@ -7823,10 +7883,10 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B87" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C87" t="s">
         <v>609</v>
@@ -7837,10 +7897,10 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B88" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C88" t="s">
         <v>609</v>
@@ -7851,7 +7911,7 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B89" t="s">
         <v>501</v>
@@ -7865,10 +7925,10 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B90" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C90" t="s">
         <v>609</v>
@@ -7879,7 +7939,7 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B91" t="s">
         <v>504</v>
@@ -7893,7 +7953,7 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B92" t="s">
         <v>504</v>
@@ -7907,7 +7967,7 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B93" t="s">
         <v>504</v>
@@ -7921,10 +7981,10 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B94" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C94" t="s">
         <v>609</v>
@@ -7935,10 +7995,10 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B95" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C95" t="s">
         <v>609</v>
@@ -7949,10 +8009,10 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B96" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C96" t="s">
         <v>609</v>
@@ -7963,10 +8023,10 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B97" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C97" t="s">
         <v>609</v>
@@ -7977,10 +8037,10 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B98" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C98" t="s">
         <v>609</v>
@@ -7991,7 +8051,7 @@
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B99" t="s">
         <v>57</v>
@@ -8001,6 +8061,34 @@
       </c>
       <c r="D99">
         <v>2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>730</v>
+      </c>
+      <c r="B100" t="s">
+        <v>580</v>
+      </c>
+      <c r="C100" t="s">
+        <v>609</v>
+      </c>
+      <c r="D100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>732</v>
+      </c>
+      <c r="B101" t="s">
+        <v>92</v>
+      </c>
+      <c r="C101" t="s">
+        <v>609</v>
+      </c>
+      <c r="D101">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -8014,7 +8102,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B287538-EFEF-41C2-B9E3-CC62272BBB45}">
-  <dimension ref="A1:E88"/>
+  <dimension ref="A1:E90"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.625" customWidth="1"/>
@@ -9044,7 +9132,7 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B72" t="s">
         <v>616</v>
@@ -9058,7 +9146,7 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B73" t="s">
         <v>617</v>
@@ -9072,10 +9160,10 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B74" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C74" t="s">
         <v>276</v>
@@ -9086,10 +9174,10 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B75" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C75" t="s">
         <v>276</v>
@@ -9100,7 +9188,7 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B76" t="s">
         <v>597</v>
@@ -9114,10 +9202,10 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B77" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C77" t="s">
         <v>276</v>
@@ -9128,10 +9216,10 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B78" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C78" t="s">
         <v>276</v>
@@ -9142,10 +9230,10 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B79" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C79" t="s">
         <v>276</v>
@@ -9156,10 +9244,10 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B80" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C80" t="s">
         <v>276</v>
@@ -9170,10 +9258,10 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B81" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C81" t="s">
         <v>276</v>
@@ -9184,10 +9272,10 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B82" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C82" t="s">
         <v>276</v>
@@ -9198,10 +9286,10 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B83" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C83" t="s">
         <v>276</v>
@@ -9212,7 +9300,7 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B84" t="s">
         <v>506</v>
@@ -9226,10 +9314,10 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B85" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="C85" t="s">
         <v>276</v>
@@ -9240,10 +9328,10 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B86" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C86" t="s">
         <v>276</v>
@@ -9254,10 +9342,10 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B87" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="C87" t="s">
         <v>276</v>
@@ -9268,15 +9356,43 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B88" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C88" t="s">
         <v>276</v>
       </c>
       <c r="D88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>730</v>
+      </c>
+      <c r="B89" t="s">
+        <v>565</v>
+      </c>
+      <c r="C89" t="s">
+        <v>276</v>
+      </c>
+      <c r="D89">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>732</v>
+      </c>
+      <c r="B90" t="s">
+        <v>735</v>
+      </c>
+      <c r="C90" t="s">
+        <v>276</v>
+      </c>
+      <c r="D90">
         <v>1</v>
       </c>
     </row>
@@ -9549,7 +9665,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B3FC0C8-1619-41FC-A1CE-6E4962B4A824}">
-  <dimension ref="A1:C57"/>
+  <dimension ref="A1:C59"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.875" bestFit="1" customWidth="1"/>
@@ -10041,6 +10157,22 @@
       </c>
       <c r="B57" t="s">
         <v>340</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>730</v>
+      </c>
+      <c r="B58" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>732</v>
+      </c>
+      <c r="B59" t="s">
+        <v>287</v>
       </c>
     </row>
   </sheetData>
@@ -10332,114 +10464,114 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B34" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B35" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B36" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B37" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B38" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B39" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B40" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B41" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B42" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B43" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B44" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B45" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B46" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B47" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
   </sheetData>
@@ -12264,7 +12396,7 @@
         <v>551</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="F78" t="s">
         <v>558</v>

--- a/db.xlsx
+++ b/db.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DS\Petro_DB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10F8B228-E12D-4ED3-A8F4-43EB7A97072B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C26538FB-7D74-4D76-BEB2-FA9443923DC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="material_master" sheetId="1" r:id="rId1"/>
-    <sheet name="route_master" sheetId="2" r:id="rId2"/>
-    <sheet name="route_input_link" sheetId="3" r:id="rId3"/>
-    <sheet name="route_output_link" sheetId="4" r:id="rId4"/>
-    <sheet name="licensor_master" sheetId="5" r:id="rId5"/>
-    <sheet name="route_licensor_link" sheetId="6" r:id="rId6"/>
-    <sheet name="supplier_master" sheetId="7" r:id="rId7"/>
-    <sheet name="material_supplier_link" sheetId="8" r:id="rId8"/>
+    <sheet name="hscode" sheetId="9" r:id="rId1"/>
+    <sheet name="material_master" sheetId="1" r:id="rId2"/>
+    <sheet name="route_master" sheetId="2" r:id="rId3"/>
+    <sheet name="route_input_link" sheetId="3" r:id="rId4"/>
+    <sheet name="route_output_link" sheetId="4" r:id="rId5"/>
+    <sheet name="licensor_master" sheetId="5" r:id="rId6"/>
+    <sheet name="route_licensor_link" sheetId="6" r:id="rId7"/>
+    <sheet name="supplier_master" sheetId="7" r:id="rId8"/>
+    <sheet name="material_supplier_link" sheetId="8" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,8 +43,62 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={6938DCE6-2658-4147-8CE7-36F1C1063B6F}</author>
+    <author>tc={5B56E149-D93C-4905-83AE-874A1A851730}</author>
+  </authors>
+  <commentList>
+    <comment ref="B3" authorId="0" shapeId="0" xr:uid="{6938DCE6-2658-4147-8CE7-36F1C1063B6F}">
+      <text>
+        <t>[스레드 댓글]
+사용 중인 버전의 Excel에서 이 스레드 댓글을 읽을 수 있지만 파일을 이후 버전의 Excel에서 열면 편집 내용이 모두 제거됩니다. 자세한 정보: https://go.microsoft.com/fwlink/?linkid=870924.
+댓글:
+    Mixed 인지 불명확</t>
+      </text>
+    </comment>
+    <comment ref="B7" authorId="1" shapeId="0" xr:uid="{5B56E149-D93C-4905-83AE-874A1A851730}">
+      <text>
+        <t>[스레드 댓글]
+사용 중인 버전의 Excel에서 이 스레드 댓글을 읽을 수 있지만 파일을 이후 버전의 Excel에서 열면 편집 내용이 모두 제거됩니다. 자세한 정보: https://go.microsoft.com/fwlink/?linkid=870924.
+댓글:
+    1-hexene인지 불분명</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={583DACAD-58E4-4A7B-BBE0-F54E7FD002A2}</author>
+    <author>tc={527C89FA-3535-45ED-AB16-7B5845EE7CC2}</author>
+  </authors>
+  <commentList>
+    <comment ref="F73" authorId="0" shapeId="0" xr:uid="{583DACAD-58E4-4A7B-BBE0-F54E7FD002A2}">
+      <text>
+        <t>[스레드 댓글]
+사용 중인 버전의 Excel에서 이 스레드 댓글을 읽을 수 있지만 파일을 이후 버전의 Excel에서 열면 편집 내용이 모두 제거됩니다. 자세한 정보: https://go.microsoft.com/fwlink/?linkid=870924.
+댓글:
+    Mixed 인지 불명확</t>
+      </text>
+    </comment>
+    <comment ref="F77" authorId="1" shapeId="0" xr:uid="{527C89FA-3535-45ED-AB16-7B5845EE7CC2}">
+      <text>
+        <t>[스레드 댓글]
+사용 중인 버전의 Excel에서 이 스레드 댓글을 읽을 수 있지만 파일을 이후 버전의 Excel에서 열면 편집 내용이 모두 제거됩니다. 자세한 정보: https://go.microsoft.com/fwlink/?linkid=870924.
+댓글:
+    1-hexene인지 불분명</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2029" uniqueCount="736">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2942" uniqueCount="845">
   <si>
     <t>remarks</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2544,10 +2599,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>블라카본코리아</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>삼남석유화학</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2564,10 +2615,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>오리온엔지니어드카본즈</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>GS칼텍스</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2643,6 +2690,374 @@
   </si>
   <si>
     <t>M095</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M089</t>
+  </si>
+  <si>
+    <t>M071</t>
+  </si>
+  <si>
+    <t>M072</t>
+  </si>
+  <si>
+    <t>M078</t>
+  </si>
+  <si>
+    <t>M079</t>
+  </si>
+  <si>
+    <t>M085</t>
+  </si>
+  <si>
+    <t>M086</t>
+  </si>
+  <si>
+    <t>hsk10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>material_name_hsk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>헥센</t>
+  </si>
+  <si>
+    <t>옥텐</t>
+  </si>
+  <si>
+    <t>시클로헥산</t>
+  </si>
+  <si>
+    <t>벤젠</t>
+  </si>
+  <si>
+    <t>톨루엔</t>
+  </si>
+  <si>
+    <t>오르토-크실렌</t>
+  </si>
+  <si>
+    <t>메타-크실렌</t>
+  </si>
+  <si>
+    <t>파라-크실렌</t>
+  </si>
+  <si>
+    <t>스티렌</t>
+  </si>
+  <si>
+    <t>에틸벤젠</t>
+  </si>
+  <si>
+    <t>큐멘</t>
+  </si>
+  <si>
+    <t>이염화에틸렌(ISO)(1,2-이염화에탄)</t>
+  </si>
+  <si>
+    <t>염화비닐(염화에틸렌)</t>
+  </si>
+  <si>
+    <t>메탄올(메틸알코올)</t>
+  </si>
+  <si>
+    <t>1-프로판올(프로필알코올)</t>
+  </si>
+  <si>
+    <t>1-부탄올(노르말-부틸알코올)</t>
+  </si>
+  <si>
+    <t>2-에틸헥실알코올</t>
+  </si>
+  <si>
+    <t>에틸렌글리콜(에탄디올)</t>
+  </si>
+  <si>
+    <t>프로필렌글리콜(프로판-1,2-디올)</t>
+  </si>
+  <si>
+    <t>페놀</t>
+  </si>
+  <si>
+    <t>4,4´-이소프로필리덴디페놀(비스페놀에이)</t>
+  </si>
+  <si>
+    <t>메틸터샤리 부틸에테르</t>
+  </si>
+  <si>
+    <t>옥시란(에틸렌옥사이드)</t>
+  </si>
+  <si>
+    <t>메틸옥시란(프로필렌옥사이드)</t>
+  </si>
+  <si>
+    <t>메탄알(포름알데히드)</t>
+  </si>
+  <si>
+    <t>에탄알(아세트알데히드)</t>
+  </si>
+  <si>
+    <t>부탄알(부티르알데히드, 노르말-이성체)</t>
+  </si>
+  <si>
+    <t>아세톤</t>
+  </si>
+  <si>
+    <t>시클로헥사논</t>
+  </si>
+  <si>
+    <t>초산</t>
+  </si>
+  <si>
+    <t>초산비닐</t>
+  </si>
+  <si>
+    <t>아크릴산</t>
+  </si>
+  <si>
+    <t>아크릴산에틸</t>
+  </si>
+  <si>
+    <t>메타아크릴산메틸</t>
+  </si>
+  <si>
+    <t>무수말레산</t>
+  </si>
+  <si>
+    <t>무수프탈산</t>
+  </si>
+  <si>
+    <t>테레프탈산</t>
+  </si>
+  <si>
+    <t>테레프탈산디메틸</t>
+  </si>
+  <si>
+    <t>아닐린</t>
+  </si>
+  <si>
+    <t>모노에탄올아민</t>
+  </si>
+  <si>
+    <t>디에탄올아민</t>
+  </si>
+  <si>
+    <t>트리에탄올아민</t>
+  </si>
+  <si>
+    <t>아크릴로니트릴</t>
+  </si>
+  <si>
+    <t>톨루엔 디이소시아네이트</t>
+  </si>
+  <si>
+    <t>디페닐메탄 디이소시아네이트</t>
+  </si>
+  <si>
+    <t>6-헥산락탐(에프시론-카프로락탐)</t>
+  </si>
+  <si>
+    <t>선형저밀도폴리에틸렌</t>
+  </si>
+  <si>
+    <t>폴리프로필렌</t>
+  </si>
+  <si>
+    <t>폴리이소부틸렌</t>
+  </si>
+  <si>
+    <t>스티렌-아크릴로니트릴 공중합체(SAN)</t>
+  </si>
+  <si>
+    <t>아크릴로니트릴-부타디엔-스티렌 공중합체(ABS)</t>
+  </si>
+  <si>
+    <t>스티렌-부타디엔 공중합체</t>
+  </si>
+  <si>
+    <t>폴리(메틸 메타크리레이트)</t>
+  </si>
+  <si>
+    <t>폴리카보네이트</t>
+  </si>
+  <si>
+    <t>폴리우레탄</t>
+  </si>
+  <si>
+    <t>변성 에틸알코올과 그 밖의 변성 주정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EPDM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Octanol</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>롯데GS화학</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구다우케미칼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S047</t>
+  </si>
+  <si>
+    <t>S048</t>
+  </si>
+  <si>
+    <t>M096</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n-Butanol</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>SSBR(123)</t>
+  </si>
+  <si>
+    <t>SSBR(100)</t>
+  </si>
+  <si>
+    <t>EPS(50)</t>
+  </si>
+  <si>
+    <t>한화토탈에너지스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HD현대케미칼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HD현대오일뱅크</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SSBR(80)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S049</t>
+  </si>
+  <si>
+    <t>대산</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OCI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>광양</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김천</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>군산</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SH에너지화학</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>삼양이노켐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>부산</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>국도화학</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인천</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SK인천석유화학</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>포항</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>삼양화성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S050</t>
+  </si>
+  <si>
+    <t>S051</t>
+  </si>
+  <si>
+    <t>S052</t>
+  </si>
+  <si>
+    <t>S053</t>
+  </si>
+  <si>
+    <t>S054</t>
+  </si>
+  <si>
+    <t>S055</t>
+  </si>
+  <si>
+    <t>EPS(100)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M073</t>
+  </si>
+  <si>
+    <t>C4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(Ethylene base)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1-butene base)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M097</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R089</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ethylene plus proplyene to EPDM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(ethylene base)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2650,7 +3065,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2679,6 +3094,13 @@
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2757,7 +3179,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2771,72 +3193,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="1"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="1"/>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="11">
     <dxf>
       <font>
         <b val="0"/>
@@ -3004,6 +3367,70 @@
         <bottom/>
       </border>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="1"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="1"/>
+          <bgColor theme="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -3017,15 +3444,37 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="이원일(W.I. Lee)" id="{8347A911-FB60-4CDD-95F5-37932B9B2DD3}" userId="S::wonil.lee90@S-OIL.COM::75f69710-ceca-4457-b198-7daa6e80130a" providerId="AD"/>
+</personList>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{58A5DC12-C774-4094-B2D2-06384F4F2631}" name="표2" displayName="표2" ref="A1:G96" totalsRowShown="0">
-  <autoFilter ref="A1:G96" xr:uid="{58A5DC12-C774-4094-B2D2-06384F4F2631}"/>
-  <tableColumns count="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{A6DFC1BB-9391-44EF-B760-6B4BD3356B2B}" name="표9" displayName="표9" ref="A1:D62" totalsRowShown="0">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C62">
+    <sortCondition ref="A1:A62"/>
+  </sortState>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{FE680477-08AA-4C50-B0E7-35C788FE9C9B}" name="material_id"/>
+    <tableColumn id="4" xr3:uid="{6A1D3365-880C-46EA-A0E9-222C9ECD36B8}" name="hsk10"/>
+    <tableColumn id="2" xr3:uid="{6CE3F1F7-BFA1-4740-AD48-075581A0AF65}" name="material_name"/>
+    <tableColumn id="3" xr3:uid="{7EC613D4-F0DE-4753-B6F0-FE8770429B48}" name="material_name_hsk" dataDxfId="10"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{58A5DC12-C774-4094-B2D2-06384F4F2631}" name="표2" displayName="표2" ref="A1:H98" totalsRowShown="0">
+  <autoFilter ref="A1:H98" xr:uid="{58A5DC12-C774-4094-B2D2-06384F4F2631}"/>
+  <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{8A7558A9-C918-4FAF-8C33-C287BE025DB3}" name="material_id"/>
     <tableColumn id="2" xr3:uid="{E0883773-7DC7-45AF-85B7-C29E7A5E523F}" name="material_name"/>
     <tableColumn id="3" xr3:uid="{8A85F034-DF3B-44C9-9E51-50661E5D53C1}" name="material_group"/>
     <tableColumn id="4" xr3:uid="{FDE30E60-A954-4DB9-B9CC-46226569A71D}" name="material_type"/>
     <tableColumn id="7" xr3:uid="{4B78A951-8AF0-41A8-98E7-8C29CB511FB6}" name="vertical_order"/>
+    <tableColumn id="8" xr3:uid="{0AD4DE31-52F7-4670-BFBF-41E8DCC216A0}" name="hsk10"/>
     <tableColumn id="5" xr3:uid="{5B491150-7223-4258-8F0C-406EC97FB36E}" name="remarks"/>
     <tableColumn id="6" xr3:uid="{4DA2D092-D5C9-4CCE-BBFA-F99BD80AF685}" name="visual_exclude"/>
   </tableColumns>
@@ -3033,9 +3482,9 @@
 </table>
 </file>
 
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8218A6AD-F328-4A1F-A40F-562BCA5E0481}" name="표1" displayName="표1" ref="A1:E89" totalsRowShown="0">
-  <autoFilter ref="A1:E89" xr:uid="{8218A6AD-F328-4A1F-A40F-562BCA5E0481}"/>
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8218A6AD-F328-4A1F-A40F-562BCA5E0481}" name="표1" displayName="표1" ref="A1:E90" totalsRowShown="0">
+  <autoFilter ref="A1:E90" xr:uid="{8218A6AD-F328-4A1F-A40F-562BCA5E0481}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{AF938E6E-C78E-4989-A143-981F636038A6}" name="route_id"/>
     <tableColumn id="2" xr3:uid="{50E61679-5C9C-455A-95D3-37527A15BDC8}" name="route_name"/>
@@ -3047,9 +3496,9 @@
 </table>
 </file>
 
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{319F947D-5803-497C-B347-524BAFE83880}" name="표3" displayName="표3" ref="A1:E101" totalsRowShown="0">
-  <autoFilter ref="A1:E101" xr:uid="{319F947D-5803-497C-B347-524BAFE83880}"/>
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{319F947D-5803-497C-B347-524BAFE83880}" name="표3" displayName="표3" ref="A1:E103" totalsRowShown="0">
+  <autoFilter ref="A1:E103" xr:uid="{319F947D-5803-497C-B347-524BAFE83880}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{37B4BF0E-EF23-494D-81CC-3F6E2B985A80}" name="route_id"/>
     <tableColumn id="2" xr3:uid="{F6F34623-0A9E-4A1B-B06B-612FA79053FF}" name="material_id"/>
@@ -3061,9 +3510,9 @@
 </table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{AE0509C7-E76F-4AAE-A013-BED08697F5A0}" name="표4" displayName="표4" ref="A1:E90" totalsRowShown="0">
-  <autoFilter ref="A1:E90" xr:uid="{AE0509C7-E76F-4AAE-A013-BED08697F5A0}"/>
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{AE0509C7-E76F-4AAE-A013-BED08697F5A0}" name="표4" displayName="표4" ref="A1:E91" totalsRowShown="0">
+  <autoFilter ref="A1:E91" xr:uid="{AE0509C7-E76F-4AAE-A013-BED08697F5A0}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{172ED76C-8FE1-403B-B64B-006301660189}" name="route_id"/>
     <tableColumn id="2" xr3:uid="{CD7417C0-560D-4558-A022-474C0791BFCE}" name="material_id"/>
@@ -3075,7 +3524,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{72485BB3-AE31-494A-94C2-315F7035CD0B}" name="표6" displayName="표6" ref="A1:C29" totalsRowShown="0">
   <autoFilter ref="A1:C29" xr:uid="{72485BB3-AE31-494A-94C2-315F7035CD0B}"/>
   <tableColumns count="3">
@@ -3087,7 +3536,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{2680B997-BCC4-46D6-8AD7-34F304E1EBEC}" name="표5" displayName="표5" ref="A1:C59" totalsRowShown="0">
   <autoFilter ref="A1:C59" xr:uid="{2680B997-BCC4-46D6-8AD7-34F304E1EBEC}"/>
   <tableColumns count="3">
@@ -3099,11 +3548,11 @@
 </table>
 </file>
 
-<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{988D0145-3F75-4766-8F22-2B7F213A0A0E}" name="표7" displayName="표7" ref="A1:C47" totalsRowShown="0" headerRowDxfId="2" tableBorderDxfId="1">
-  <autoFilter ref="A1:C47" xr:uid="{988D0145-3F75-4766-8F22-2B7F213A0A0E}"/>
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{988D0145-3F75-4766-8F22-2B7F213A0A0E}" name="표7" displayName="표7" ref="A1:C56" totalsRowShown="0" headerRowDxfId="9" tableBorderDxfId="8">
+  <autoFilter ref="A1:C56" xr:uid="{988D0145-3F75-4766-8F22-2B7F213A0A0E}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{6BB3C325-E378-494B-8658-DFA03BEE5EC2}" name="supplier_id" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{6BB3C325-E378-494B-8658-DFA03BEE5EC2}" name="supplier_id" dataDxfId="7"/>
     <tableColumn id="2" xr3:uid="{DEA6BFD5-F301-478A-8C32-60D29F64785D}" name="supplier_name"/>
     <tableColumn id="3" xr3:uid="{BC1D1EDC-ADC4-4D1E-A0A8-CF82814F5708}" name="remark"/>
   </tableColumns>
@@ -3111,15 +3560,15 @@
 </table>
 </file>
 
-<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{6FFBAFCB-1352-4E9C-9D70-4E9F53000FD3}" name="표8" displayName="표8" ref="A1:H78" totalsRowShown="0" headerRowDxfId="9" tableBorderDxfId="8">
-  <autoFilter ref="A1:H78" xr:uid="{6FFBAFCB-1352-4E9C-9D70-4E9F53000FD3}"/>
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{6FFBAFCB-1352-4E9C-9D70-4E9F53000FD3}" name="표8" displayName="표8" ref="A1:H226" totalsRowShown="0" headerRowDxfId="6" tableBorderDxfId="5">
+  <autoFilter ref="A1:H226" xr:uid="{6FFBAFCB-1352-4E9C-9D70-4E9F53000FD3}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{12F0CAA4-2E26-489B-9552-16FE76A428C0}" name="material_id" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{42641D2C-48F0-4482-B991-D8C701A4A414}" name="supplier_id" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{7C63F152-DC19-490F-BEE8-B2DDA5A0A3C6}" name="estimated_capacity" dataDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{79A6CA5E-5ABE-473D-A0BF-3AD3ED75DDBE}" name="capacity_unit" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{0715DE87-36F5-4FBB-8E82-58C22846AD76}" name="location" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{12F0CAA4-2E26-489B-9552-16FE76A428C0}" name="material_id" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{42641D2C-48F0-4482-B991-D8C701A4A414}" name="supplier_id" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{7C63F152-DC19-490F-BEE8-B2DDA5A0A3C6}" name="estimated_capacity" dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{79A6CA5E-5ABE-473D-A0BF-3AD3ED75DDBE}" name="capacity_unit" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{0715DE87-36F5-4FBB-8E82-58C22846AD76}" name="location" dataDxfId="0"/>
     <tableColumn id="5" xr3:uid="{1CD33AA1-B102-4408-AF4D-6DF4634950F5}" name="source_type"/>
     <tableColumn id="10" xr3:uid="{75C980CA-1009-4854-A174-027876A8AF39}" name="source_year"/>
     <tableColumn id="6" xr3:uid="{D155A232-0361-4D95-A82D-5D68EA1F8A6B}" name="remarks"/>
@@ -3389,20 +3838,732 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="B3" dT="2026-04-07T05:11:03.73" personId="{8347A911-FB60-4CDD-95F5-37932B9B2DD3}" id="{6938DCE6-2658-4147-8CE7-36F1C1063B6F}">
+    <text>Mixed 인지 불명확</text>
+  </threadedComment>
+  <threadedComment ref="B7" dT="2026-04-07T05:12:26.45" personId="{8347A911-FB60-4CDD-95F5-37932B9B2DD3}" id="{5B56E149-D93C-4905-83AE-874A1A851730}">
+    <text>1-hexene인지 불분명</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="F73" dT="2026-04-07T05:11:03.73" personId="{8347A911-FB60-4CDD-95F5-37932B9B2DD3}" id="{583DACAD-58E4-4A7B-BBE0-F54E7FD002A2}">
+    <text>Mixed 인지 불명확</text>
+  </threadedComment>
+  <threadedComment ref="F77" dT="2026-04-07T05:12:26.45" personId="{8347A911-FB60-4CDD-95F5-37932B9B2DD3}" id="{527C89FA-3535-45ED-AB16-7B5845EE7CC2}">
+    <text>1-hexene인지 불분명</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G96"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E43BD60A-1BAE-4F7A-A103-6798E483213F}">
+  <dimension ref="A1:D62"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="12.625" customWidth="1"/>
+    <col min="3" max="3" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>741</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B2">
+        <v>2207200000</v>
+      </c>
+      <c r="C2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B3" s="11">
+        <v>2707300000</v>
+      </c>
+      <c r="C3" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B4">
+        <v>2901210000</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B5">
+        <v>2901220000</v>
+      </c>
+      <c r="C5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B6">
+        <v>2901241000</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B7">
+        <v>2901291000</v>
+      </c>
+      <c r="C7" t="s">
+        <v>568</v>
+      </c>
+      <c r="D7" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B8">
+        <v>2901292000</v>
+      </c>
+      <c r="C8" t="s">
+        <v>732</v>
+      </c>
+      <c r="D8" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B9">
+        <v>2902110000</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D9" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B10">
+        <v>2902200000</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B11">
+        <v>2902300000</v>
+      </c>
+      <c r="C11" t="s">
+        <v>503</v>
+      </c>
+      <c r="D11" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B12">
+        <v>2902410000</v>
+      </c>
+      <c r="C12" t="s">
+        <v>667</v>
+      </c>
+      <c r="D12" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B13">
+        <v>2902420000</v>
+      </c>
+      <c r="C13" t="s">
+        <v>668</v>
+      </c>
+      <c r="D13" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B14">
+        <v>2902430000</v>
+      </c>
+      <c r="C14" t="s">
+        <v>669</v>
+      </c>
+      <c r="D14" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B15">
+        <v>2902500000</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B16">
+        <v>2902600000</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B17">
+        <v>2902700000</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B18">
+        <v>2903150000</v>
+      </c>
+      <c r="C18" t="s">
+        <v>474</v>
+      </c>
+      <c r="D18" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B19">
+        <v>2903210000</v>
+      </c>
+      <c r="C19" t="s">
+        <v>49</v>
+      </c>
+      <c r="D19" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B20">
+        <v>2905110000</v>
+      </c>
+      <c r="C20" t="s">
+        <v>473</v>
+      </c>
+      <c r="D20" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B21">
+        <v>2905121000</v>
+      </c>
+      <c r="C21" t="s">
+        <v>476</v>
+      </c>
+      <c r="D21" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B22">
+        <v>2905130000</v>
+      </c>
+      <c r="C22" t="s">
+        <v>108</v>
+      </c>
+      <c r="D22" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B23">
+        <v>2905161000</v>
+      </c>
+      <c r="C23" t="s">
+        <v>114</v>
+      </c>
+      <c r="D23" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B24">
+        <v>2905310000</v>
+      </c>
+      <c r="C24" t="s">
+        <v>494</v>
+      </c>
+      <c r="D24" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B25">
+        <v>2905320000</v>
+      </c>
+      <c r="C25" t="s">
+        <v>278</v>
+      </c>
+      <c r="D25" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B26">
+        <v>2907111000</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D26" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B27">
+        <v>2907231000</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="D27" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B28">
+        <v>2909192000</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D28" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B29">
+        <v>2910100000</v>
+      </c>
+      <c r="C29" t="s">
+        <v>486</v>
+      </c>
+      <c r="D29" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B30">
+        <v>2910200000</v>
+      </c>
+      <c r="C30" t="s">
+        <v>280</v>
+      </c>
+      <c r="D30" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B31">
+        <v>2912110000</v>
+      </c>
+      <c r="C31" t="s">
+        <v>613</v>
+      </c>
+      <c r="D31" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B32">
+        <v>2912120000</v>
+      </c>
+      <c r="C32" t="s">
+        <v>39</v>
+      </c>
+      <c r="D32" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B33">
+        <v>2912193000</v>
+      </c>
+      <c r="C33" t="s">
+        <v>107</v>
+      </c>
+      <c r="D33" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B34">
+        <v>2914110000</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D34" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B35">
+        <v>2914221000</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="D35" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B36">
+        <v>2915210000</v>
+      </c>
+      <c r="C36" t="s">
+        <v>477</v>
+      </c>
+      <c r="D36" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B37">
+        <v>2915310000</v>
+      </c>
+      <c r="C37" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B38">
+        <v>2915320000</v>
+      </c>
+      <c r="C38" t="s">
+        <v>50</v>
+      </c>
+      <c r="D38" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B39">
+        <v>2916111000</v>
+      </c>
+      <c r="C39" t="s">
+        <v>103</v>
+      </c>
+      <c r="D39" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B40">
+        <v>2916121000</v>
+      </c>
+      <c r="C40" t="s">
+        <v>38</v>
+      </c>
+      <c r="D40" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B41">
+        <v>2916141000</v>
+      </c>
+      <c r="C41" t="s">
+        <v>599</v>
+      </c>
+      <c r="D41" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B42">
+        <v>2917140000</v>
+      </c>
+      <c r="C42" t="s">
+        <v>472</v>
+      </c>
+      <c r="D42" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B43">
+        <v>2917350000</v>
+      </c>
+      <c r="C43" t="s">
+        <v>507</v>
+      </c>
+      <c r="D43" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B44">
+        <v>2917361000</v>
+      </c>
+      <c r="C44" t="s">
+        <v>512</v>
+      </c>
+      <c r="D44" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B45">
+        <v>2917370000</v>
+      </c>
+      <c r="C45" t="s">
+        <v>513</v>
+      </c>
+      <c r="D45" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B46">
+        <v>2921411000</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D46" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B47">
+        <v>2922111000</v>
+      </c>
+      <c r="C47" t="s">
+        <v>46</v>
+      </c>
+      <c r="D47" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="48" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B48">
+        <v>2922121000</v>
+      </c>
+      <c r="C48" t="s">
+        <v>47</v>
+      </c>
+      <c r="D48" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B49">
+        <v>2922150000</v>
+      </c>
+      <c r="C49" t="s">
+        <v>48</v>
+      </c>
+      <c r="D49" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B50">
+        <v>2926100000</v>
+      </c>
+      <c r="C50" t="s">
+        <v>475</v>
+      </c>
+      <c r="D50" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="51" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B51">
+        <v>2929101000</v>
+      </c>
+      <c r="C51" t="s">
+        <v>650</v>
+      </c>
+      <c r="D51" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="52" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B52">
+        <v>2929102000</v>
+      </c>
+      <c r="C52" t="s">
+        <v>649</v>
+      </c>
+      <c r="D52" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="53" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B53">
+        <v>2933710000</v>
+      </c>
+      <c r="C53" t="s">
+        <v>563</v>
+      </c>
+      <c r="D53" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="54" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B54">
+        <v>3901101000</v>
+      </c>
+      <c r="C54" t="s">
+        <v>33</v>
+      </c>
+      <c r="D54" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="55" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B55">
+        <v>3902100000</v>
+      </c>
+      <c r="C55" t="s">
+        <v>281</v>
+      </c>
+      <c r="D55" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="56" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B56">
+        <v>3902200000</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="D56" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="57" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B57">
+        <v>3903200000</v>
+      </c>
+      <c r="C57" t="s">
+        <v>112</v>
+      </c>
+      <c r="D57" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="58" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B58">
+        <v>3903300000</v>
+      </c>
+      <c r="C58" t="s">
+        <v>111</v>
+      </c>
+      <c r="D58" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="59" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B59">
+        <v>3903901000</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D59" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="60" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B60">
+        <v>3906100000</v>
+      </c>
+      <c r="C60" t="s">
+        <v>600</v>
+      </c>
+      <c r="D60" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="61" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B61">
+        <v>3907400000</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="D61" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="62" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B62">
+        <v>3909500000</v>
+      </c>
+      <c r="C62" t="s">
+        <v>282</v>
+      </c>
+      <c r="D62" t="s">
+        <v>798</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H99"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28.125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="30.375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="12.625" customWidth="1"/>
+    <col min="7" max="7" width="16.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -3419,13 +4580,16 @@
         <v>559</v>
       </c>
       <c r="F1" t="s">
+        <v>741</v>
+      </c>
+      <c r="G1" t="s">
         <v>0</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -3441,11 +4605,14 @@
       <c r="E2">
         <v>2100</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2">
+        <v>2901210000</v>
+      </c>
+      <c r="G2" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>51</v>
       </c>
@@ -3462,7 +4629,7 @@
         <v>2110</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -3479,7 +4646,7 @@
         <v>2120</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -3495,8 +4662,11 @@
       <c r="E5">
         <v>2130</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F5">
+        <v>3901101000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -3512,11 +4682,14 @@
       <c r="E6">
         <v>2200</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6">
+        <v>2903150000</v>
+      </c>
+      <c r="G6" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -3532,11 +4705,14 @@
       <c r="E7">
         <v>2210</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7">
+        <v>2903210000</v>
+      </c>
+      <c r="G7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -3552,11 +4728,11 @@
       <c r="E8">
         <v>2220</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -3572,8 +4748,11 @@
       <c r="E9">
         <v>2400</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F9">
+        <v>2207200000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -3589,11 +4768,11 @@
       <c r="E10">
         <v>2500</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -3609,8 +4788,11 @@
       <c r="E11">
         <v>2420</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F11">
+        <v>2915310000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -3626,8 +4808,11 @@
       <c r="E12">
         <v>2510</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F12">
+        <v>2916121000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>52</v>
       </c>
@@ -3643,11 +4828,14 @@
       <c r="E13">
         <v>2300</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13">
+        <v>2910100000</v>
+      </c>
+      <c r="G13" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>53</v>
       </c>
@@ -3663,11 +4851,11 @@
       <c r="E14">
         <v>2310</v>
       </c>
-      <c r="G14" t="s">
+      <c r="H14" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>54</v>
       </c>
@@ -3683,11 +4871,14 @@
       <c r="E15">
         <v>2320</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15">
+        <v>2922111000</v>
+      </c>
+      <c r="G15" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>55</v>
       </c>
@@ -3703,11 +4894,14 @@
       <c r="E16">
         <v>2330</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16">
+        <v>2922121000</v>
+      </c>
+      <c r="G16" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>56</v>
       </c>
@@ -3723,11 +4917,14 @@
       <c r="E17">
         <v>2340</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17">
+        <v>2922150000</v>
+      </c>
+      <c r="G17" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>57</v>
       </c>
@@ -3743,11 +4940,14 @@
       <c r="E18">
         <v>2380</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18">
+        <v>2905310000</v>
+      </c>
+      <c r="G18" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>58</v>
       </c>
@@ -3763,11 +4963,14 @@
       <c r="E19">
         <v>2410</v>
       </c>
-      <c r="G19" t="s">
+      <c r="F19">
+        <v>2912120000</v>
+      </c>
+      <c r="H19" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>59</v>
       </c>
@@ -3783,11 +4986,14 @@
       <c r="E20">
         <v>2600</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F20">
+        <v>2915320000</v>
+      </c>
+      <c r="G20" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>60</v>
       </c>
@@ -3803,11 +5009,14 @@
       <c r="E21">
         <v>3100</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F21">
+        <v>2901220000</v>
+      </c>
+      <c r="G21" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>61</v>
       </c>
@@ -3823,11 +5032,14 @@
       <c r="E22">
         <v>3200</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F22">
+        <v>2926100000</v>
+      </c>
+      <c r="G22" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>62</v>
       </c>
@@ -3843,11 +5055,14 @@
       <c r="E23">
         <v>3210</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F23">
+        <v>3903300000</v>
+      </c>
+      <c r="G23" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>63</v>
       </c>
@@ -3863,14 +5078,17 @@
       <c r="E24">
         <v>3220</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F24">
+        <v>3903200000</v>
+      </c>
+      <c r="G24" t="s">
         <v>496</v>
       </c>
-      <c r="G24" t="s">
+      <c r="H24" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>64</v>
       </c>
@@ -3886,11 +5104,11 @@
       <c r="E25">
         <v>3230</v>
       </c>
-      <c r="F25" t="s">
+      <c r="G25" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>65</v>
       </c>
@@ -3906,11 +5124,14 @@
       <c r="E26">
         <v>3110</v>
       </c>
-      <c r="F26" t="s">
+      <c r="F26">
+        <v>3902100000</v>
+      </c>
+      <c r="G26" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>66</v>
       </c>
@@ -3926,11 +5147,14 @@
       <c r="E27">
         <v>3300</v>
       </c>
-      <c r="F27" t="s">
+      <c r="F27">
+        <v>2910200000</v>
+      </c>
+      <c r="G27" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>67</v>
       </c>
@@ -3946,11 +5170,14 @@
       <c r="E28">
         <v>3310</v>
       </c>
-      <c r="F28" t="s">
+      <c r="F28">
+        <v>2905320000</v>
+      </c>
+      <c r="G28" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>68</v>
       </c>
@@ -3966,11 +5193,11 @@
       <c r="E29">
         <v>3320</v>
       </c>
-      <c r="F29" t="s">
+      <c r="G29" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>69</v>
       </c>
@@ -3987,7 +5214,7 @@
         <v>3330</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>70</v>
       </c>
@@ -4003,11 +5230,14 @@
       <c r="E31">
         <v>3340</v>
       </c>
-      <c r="F31" t="s">
+      <c r="F31">
+        <v>3909500000</v>
+      </c>
+      <c r="G31" t="s">
         <v>698</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>71</v>
       </c>
@@ -4023,11 +5253,14 @@
       <c r="E32">
         <v>3400</v>
       </c>
-      <c r="F32" t="s">
+      <c r="F32">
+        <v>2916111000</v>
+      </c>
+      <c r="G32" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>72</v>
       </c>
@@ -4044,7 +5277,7 @@
         <v>3420</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>73</v>
       </c>
@@ -4061,7 +5294,7 @@
         <v>3410</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>74</v>
       </c>
@@ -4077,11 +5310,11 @@
       <c r="E35">
         <v>3430</v>
       </c>
-      <c r="F35" t="s">
+      <c r="G35" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>75</v>
       </c>
@@ -4097,8 +5330,11 @@
       <c r="E36">
         <v>3500</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F36">
+        <v>2912193000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>76</v>
       </c>
@@ -4114,13 +5350,19 @@
       <c r="E37">
         <v>3520</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F37">
+        <v>2905161000</v>
+      </c>
+      <c r="G37" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>77</v>
       </c>
       <c r="B38" t="s">
-        <v>108</v>
+        <v>807</v>
       </c>
       <c r="C38" t="s">
         <v>8</v>
@@ -4131,8 +5373,11 @@
       <c r="E38">
         <v>3510</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F38">
+        <v>2905130000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>78</v>
       </c>
@@ -4149,7 +5394,7 @@
         <v>3530</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>79</v>
       </c>
@@ -4166,7 +5411,7 @@
         <v>3700</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>80</v>
       </c>
@@ -4183,7 +5428,7 @@
         <v>3710</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>81</v>
       </c>
@@ -4199,11 +5444,14 @@
       <c r="E42">
         <v>3600</v>
       </c>
-      <c r="F42" t="s">
+      <c r="F42">
+        <v>2905121000</v>
+      </c>
+      <c r="G42" t="s">
         <v>560</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>82</v>
       </c>
@@ -4219,8 +5467,11 @@
       <c r="E43">
         <v>3610</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F43" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>83</v>
       </c>
@@ -4236,11 +5487,14 @@
       <c r="E44" s="1">
         <v>4100</v>
       </c>
-      <c r="F44" t="s">
+      <c r="F44">
+        <v>2901241000</v>
+      </c>
+      <c r="G44" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>84</v>
       </c>
@@ -4257,7 +5511,7 @@
         <v>4110</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>85</v>
       </c>
@@ -4273,8 +5527,11 @@
       <c r="E46" s="1">
         <v>4120</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F46">
+        <v>3903901000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>86</v>
       </c>
@@ -4291,7 +5548,7 @@
         <v>4200</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>87</v>
       </c>
@@ -4307,11 +5564,14 @@
       <c r="E48" s="1">
         <v>4210</v>
       </c>
-      <c r="F48" s="1" t="s">
+      <c r="F48">
+        <v>3902200000</v>
+      </c>
+      <c r="G48" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>88</v>
       </c>
@@ -4327,11 +5587,11 @@
       <c r="E49" s="1">
         <v>4330</v>
       </c>
-      <c r="F49" s="1" t="s">
+      <c r="G49" s="1" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>89</v>
       </c>
@@ -4347,8 +5607,11 @@
       <c r="E50" s="1">
         <v>4230</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F50">
+        <v>2909192000</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>90</v>
       </c>
@@ -4364,11 +5627,11 @@
       <c r="E51" s="1">
         <v>4220</v>
       </c>
-      <c r="G51" t="s">
+      <c r="H51" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>91</v>
       </c>
@@ -4385,7 +5648,7 @@
         <v>4300</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>92</v>
       </c>
@@ -4402,7 +5665,7 @@
         <v>4310</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>93</v>
       </c>
@@ -4419,7 +5682,7 @@
         <v>4320</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>94</v>
       </c>
@@ -4435,9 +5698,12 @@
       <c r="E55" s="1">
         <v>6000</v>
       </c>
-      <c r="F55" s="1"/>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F55">
+        <v>2902200000</v>
+      </c>
+      <c r="G55" s="1"/>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>127</v>
       </c>
@@ -4453,11 +5719,14 @@
       <c r="E56" s="1">
         <v>6100</v>
       </c>
-      <c r="F56" s="1" t="s">
+      <c r="F56">
+        <v>2902600000</v>
+      </c>
+      <c r="G56" s="1" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>128</v>
       </c>
@@ -4473,9 +5742,12 @@
       <c r="E57" s="1">
         <v>6110</v>
       </c>
-      <c r="F57" s="1"/>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F57">
+        <v>2902500000</v>
+      </c>
+      <c r="G57" s="1"/>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>134</v>
       </c>
@@ -4491,11 +5763,11 @@
       <c r="E58" s="1">
         <v>6120</v>
       </c>
-      <c r="F58" s="1" t="s">
+      <c r="G58" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>135</v>
       </c>
@@ -4511,9 +5783,12 @@
       <c r="E59" s="1">
         <v>6200</v>
       </c>
-      <c r="F59" s="1"/>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F59">
+        <v>2902700000</v>
+      </c>
+      <c r="G59" s="1"/>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>136</v>
       </c>
@@ -4529,9 +5804,12 @@
       <c r="E60" s="1">
         <v>6210</v>
       </c>
-      <c r="F60" s="1"/>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F60">
+        <v>2907111000</v>
+      </c>
+      <c r="G60" s="1"/>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>137</v>
       </c>
@@ -4547,9 +5825,12 @@
       <c r="E61" s="1">
         <v>6220</v>
       </c>
-      <c r="F61" s="1"/>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F61">
+        <v>2914110000</v>
+      </c>
+      <c r="G61" s="1"/>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>138</v>
       </c>
@@ -4565,11 +5846,14 @@
       <c r="E62" s="1">
         <v>6230</v>
       </c>
-      <c r="F62" s="1" t="s">
+      <c r="F62">
+        <v>2907231000</v>
+      </c>
+      <c r="G62" s="1" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>139</v>
       </c>
@@ -4585,11 +5869,14 @@
       <c r="E63" s="1">
         <v>6240</v>
       </c>
-      <c r="F63" s="1" t="s">
+      <c r="F63">
+        <v>3907400000</v>
+      </c>
+      <c r="G63" s="1" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>140</v>
       </c>
@@ -4605,9 +5892,9 @@
       <c r="E64" s="1">
         <v>6250</v>
       </c>
-      <c r="F64" s="1"/>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G64" s="1"/>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>141</v>
       </c>
@@ -4623,9 +5910,12 @@
       <c r="E65" s="1">
         <v>6300</v>
       </c>
-      <c r="F65" s="1"/>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F65">
+        <v>2902110000</v>
+      </c>
+      <c r="G65" s="1"/>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>142</v>
       </c>
@@ -4641,9 +5931,12 @@
       <c r="E66" s="1">
         <v>6320</v>
       </c>
-      <c r="F66" s="1"/>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F66">
+        <v>2921411000</v>
+      </c>
+      <c r="G66" s="1"/>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>143</v>
       </c>
@@ -4659,11 +5952,11 @@
       <c r="E67" s="1">
         <v>6400</v>
       </c>
-      <c r="F67" t="s">
+      <c r="G67" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>400</v>
       </c>
@@ -4679,9 +5972,12 @@
       <c r="E68" s="1">
         <v>6310</v>
       </c>
-      <c r="F68" s="1"/>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F68">
+        <v>2914221000</v>
+      </c>
+      <c r="G68" s="1"/>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>479</v>
       </c>
@@ -4697,11 +5993,14 @@
       <c r="E69">
         <v>6500</v>
       </c>
-      <c r="F69" t="s">
+      <c r="F69">
+        <v>2917140000</v>
+      </c>
+      <c r="G69" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>498</v>
       </c>
@@ -4717,8 +6016,11 @@
       <c r="E70">
         <v>100</v>
       </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F70">
+        <v>2905110000</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>500</v>
       </c>
@@ -4734,8 +6036,11 @@
       <c r="E71">
         <v>200</v>
       </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F71">
+        <v>2915210000</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>501</v>
       </c>
@@ -4751,8 +6056,11 @@
       <c r="E72">
         <v>7000</v>
       </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F72">
+        <v>2902300000</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>504</v>
       </c>
@@ -4768,8 +6076,11 @@
       <c r="E73">
         <v>8000</v>
       </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F73" s="11">
+        <v>2707300000</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>506</v>
       </c>
@@ -4785,11 +6096,14 @@
       <c r="E74">
         <v>8110</v>
       </c>
-      <c r="F74" t="s">
+      <c r="F74">
+        <v>2917350000</v>
+      </c>
+      <c r="G74" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>517</v>
       </c>
@@ -4805,8 +6119,11 @@
       <c r="E75">
         <v>6330</v>
       </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F75">
+        <v>2933710000</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>564</v>
       </c>
@@ -4822,11 +6139,11 @@
       <c r="E76">
         <v>2700</v>
       </c>
-      <c r="F76" t="s">
+      <c r="G76" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>565</v>
       </c>
@@ -4840,10 +6157,16 @@
         <v>509</v>
       </c>
       <c r="E77">
-        <v>2710</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+        <v>2900</v>
+      </c>
+      <c r="F77">
+        <v>2901291000</v>
+      </c>
+      <c r="G77" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>566</v>
       </c>
@@ -4860,7 +6183,7 @@
         <v>2720</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>597</v>
       </c>
@@ -4876,11 +6199,14 @@
       <c r="E79">
         <v>400</v>
       </c>
-      <c r="F79" t="s">
+      <c r="F79">
+        <v>2916141000</v>
+      </c>
+      <c r="G79" t="s">
         <v>603</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>598</v>
       </c>
@@ -4896,11 +6222,14 @@
       <c r="E80">
         <v>410</v>
       </c>
-      <c r="F80" t="s">
+      <c r="F80">
+        <v>3906100000</v>
+      </c>
+      <c r="G80" t="s">
         <v>602</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>612</v>
       </c>
@@ -4916,11 +6245,14 @@
       <c r="E81">
         <v>300</v>
       </c>
-      <c r="F81" t="s">
+      <c r="F81">
+        <v>2912110000</v>
+      </c>
+      <c r="G81" t="s">
         <v>602</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>616</v>
       </c>
@@ -4936,11 +6268,11 @@
       <c r="E82">
         <v>2360</v>
       </c>
-      <c r="F82" t="s">
+      <c r="G82" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>617</v>
       </c>
@@ -4956,11 +6288,11 @@
       <c r="E83">
         <v>2370</v>
       </c>
-      <c r="F83" t="s">
+      <c r="G83" t="s">
         <v>621</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>630</v>
       </c>
@@ -4976,11 +6308,11 @@
       <c r="E84">
         <v>2610</v>
       </c>
-      <c r="F84" t="s">
+      <c r="G84" t="s">
         <v>634</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>631</v>
       </c>
@@ -4996,11 +6328,11 @@
       <c r="E85">
         <v>2620</v>
       </c>
-      <c r="F85" t="s">
+      <c r="G85" t="s">
         <v>635</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>647</v>
       </c>
@@ -5016,11 +6348,14 @@
       <c r="E86">
         <v>6410</v>
       </c>
-      <c r="F86" t="s">
+      <c r="F86">
+        <v>2929102000</v>
+      </c>
+      <c r="G86" t="s">
         <v>651</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>648</v>
       </c>
@@ -5036,11 +6371,14 @@
       <c r="E87">
         <v>7100</v>
       </c>
-      <c r="F87" t="s">
+      <c r="F87">
+        <v>2929101000</v>
+      </c>
+      <c r="G87" t="s">
         <v>652</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>664</v>
       </c>
@@ -5056,11 +6394,14 @@
       <c r="E88">
         <v>8100</v>
       </c>
-      <c r="F88" t="s">
+      <c r="F88">
+        <v>2902410000</v>
+      </c>
+      <c r="G88" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>665</v>
       </c>
@@ -5076,11 +6417,14 @@
       <c r="E89">
         <v>8200</v>
       </c>
-      <c r="F89" t="s">
+      <c r="F89">
+        <v>2902420000</v>
+      </c>
+      <c r="G89" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>666</v>
       </c>
@@ -5096,11 +6440,14 @@
       <c r="E90">
         <v>8300</v>
       </c>
-      <c r="F90" t="s">
+      <c r="F90">
+        <v>2902430000</v>
+      </c>
+      <c r="G90" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>685</v>
       </c>
@@ -5116,11 +6463,11 @@
       <c r="E91">
         <v>8210</v>
       </c>
-      <c r="F91" t="s">
+      <c r="G91" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>686</v>
       </c>
@@ -5136,11 +6483,14 @@
       <c r="E92">
         <v>8310</v>
       </c>
-      <c r="F92" t="s">
+      <c r="F92">
+        <v>2917361000</v>
+      </c>
+      <c r="G92" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>687</v>
       </c>
@@ -5156,11 +6506,14 @@
       <c r="E93">
         <v>8320</v>
       </c>
-      <c r="F93" t="s">
+      <c r="F93">
+        <v>2917370000</v>
+      </c>
+      <c r="G93" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>689</v>
       </c>
@@ -5176,11 +6529,11 @@
       <c r="E94">
         <v>8330</v>
       </c>
-      <c r="F94" t="s">
+      <c r="G94" t="s">
         <v>691</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>700</v>
       </c>
@@ -5196,25 +6549,73 @@
       <c r="E95">
         <v>3350</v>
       </c>
-      <c r="F95" t="s">
+      <c r="F95">
+        <v>3909500000</v>
+      </c>
+      <c r="G95" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="B96" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="C96" t="s">
-        <v>569</v>
+        <v>838</v>
       </c>
       <c r="D96" t="s">
         <v>509</v>
       </c>
       <c r="E96">
-        <v>2730</v>
+        <v>4350</v>
+      </c>
+      <c r="F96">
+        <v>2901292000</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>806</v>
+      </c>
+      <c r="B97" t="s">
+        <v>568</v>
+      </c>
+      <c r="C97" t="s">
+        <v>838</v>
+      </c>
+      <c r="D97" t="s">
+        <v>509</v>
+      </c>
+      <c r="E97">
+        <v>4340</v>
+      </c>
+      <c r="G97" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>841</v>
+      </c>
+      <c r="B98" t="s">
+        <v>800</v>
+      </c>
+      <c r="C98" t="s">
+        <v>569</v>
+      </c>
+      <c r="D98" t="s">
+        <v>601</v>
+      </c>
+      <c r="E98">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B99" s="12" t="s">
+        <v>808</v>
       </c>
     </row>
   </sheetData>
@@ -5223,15 +6624,16 @@
   <headerFooter>
     <oddFooter>&amp;L_x000D_&amp;1#&amp;"Aptos"&amp;11&amp;K000000 S-OIL: General</oddFooter>
   </headerFooter>
+  <legacyDrawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD555547-6CA4-43C0-947A-5034E027DB5A}">
-  <dimension ref="A1:E89"/>
+  <dimension ref="A1:E90"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.875" bestFit="1" customWidth="1"/>
@@ -6185,6 +7587,9 @@
       <c r="D63">
         <v>2</v>
       </c>
+      <c r="E63" t="s">
+        <v>840</v>
+      </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
@@ -6548,10 +7953,10 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="B88" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="C88" t="s">
         <v>577</v>
@@ -6559,19 +7964,39 @@
       <c r="D88">
         <v>1</v>
       </c>
+      <c r="E88" t="s">
+        <v>844</v>
+      </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="B89" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="C89" t="s">
         <v>577</v>
       </c>
       <c r="D89">
         <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>842</v>
+      </c>
+      <c r="B90" t="s">
+        <v>843</v>
+      </c>
+      <c r="C90" t="s">
+        <v>585</v>
+      </c>
+      <c r="D90">
+        <v>1</v>
+      </c>
+      <c r="E90" t="s">
+        <v>693</v>
       </c>
     </row>
   </sheetData>
@@ -6584,9 +8009,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDFAB716-5D9E-4323-B5B0-31948BE7F75C}">
-  <dimension ref="A1:E101"/>
+  <dimension ref="A1:E103"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.875" bestFit="1" customWidth="1"/>
@@ -8065,7 +9490,7 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="B100" t="s">
         <v>580</v>
@@ -8079,7 +9504,7 @@
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="B101" t="s">
         <v>92</v>
@@ -8089,6 +9514,34 @@
       </c>
       <c r="D101">
         <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>842</v>
+      </c>
+      <c r="B102" t="s">
+        <v>580</v>
+      </c>
+      <c r="C102" t="s">
+        <v>609</v>
+      </c>
+      <c r="D102">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>842</v>
+      </c>
+      <c r="B103" t="s">
+        <v>540</v>
+      </c>
+      <c r="C103" t="s">
+        <v>581</v>
+      </c>
+      <c r="D103">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -8100,9 +9553,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B287538-EFEF-41C2-B9E3-CC62272BBB45}">
-  <dimension ref="A1:E90"/>
+  <dimension ref="A1:E91"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.625" customWidth="1"/>
@@ -9023,7 +10476,7 @@
         <v>571</v>
       </c>
       <c r="B64" t="s">
-        <v>565</v>
+        <v>806</v>
       </c>
       <c r="C64" t="s">
         <v>276</v>
@@ -9370,7 +10823,7 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="B89" t="s">
         <v>565</v>
@@ -9384,15 +10837,29 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="B90" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="C90" t="s">
         <v>276</v>
       </c>
       <c r="D90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>842</v>
+      </c>
+      <c r="B91" t="s">
+        <v>841</v>
+      </c>
+      <c r="C91" t="s">
+        <v>276</v>
+      </c>
+      <c r="D91">
         <v>1</v>
       </c>
     </row>
@@ -9405,7 +10872,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DC2F6D2-CC24-4843-AC85-17C15B0B1CF5}">
   <dimension ref="A1:C29"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -9663,7 +11130,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B3FC0C8-1619-41FC-A1CE-6E4962B4A824}">
   <dimension ref="A1:C59"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -10161,7 +11628,7 @@
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="B58" t="s">
         <v>287</v>
@@ -10169,409 +11636,10 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="B59" t="s">
         <v>287</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{867694C3-947A-415D-8A10-3CC2EBC6A1B4}">
-  <dimension ref="A1:C47"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="12.125" customWidth="1"/>
-    <col min="2" max="2" width="15.375" customWidth="1"/>
-    <col min="3" max="3" width="9" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
-        <v>403</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>404</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>419</v>
-      </c>
-      <c r="C2" s="4"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>409</v>
-      </c>
-      <c r="B3" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="B4" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>411</v>
-      </c>
-      <c r="B5" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="B6" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>413</v>
-      </c>
-      <c r="B7" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="B8" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>415</v>
-      </c>
-      <c r="B9" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="B10" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>417</v>
-      </c>
-      <c r="B11" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="B12" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>449</v>
-      </c>
-      <c r="B13" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="B14" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>451</v>
-      </c>
-      <c r="B15" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="B16" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>453</v>
-      </c>
-      <c r="B17" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="B18" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>455</v>
-      </c>
-      <c r="B19" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="B20" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>457</v>
-      </c>
-      <c r="B21" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="B22" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>459</v>
-      </c>
-      <c r="B23" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="B24" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>461</v>
-      </c>
-      <c r="B25" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="B26" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>463</v>
-      </c>
-      <c r="B27" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="B28" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>465</v>
-      </c>
-      <c r="B29" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="B30" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>467</v>
-      </c>
-      <c r="B31" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="B32" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="B33" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
-        <v>715</v>
-      </c>
-      <c r="B34" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
-        <v>716</v>
-      </c>
-      <c r="B35" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
-        <v>717</v>
-      </c>
-      <c r="B36" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
-        <v>718</v>
-      </c>
-      <c r="B37" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
-        <v>719</v>
-      </c>
-      <c r="B38" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
-        <v>720</v>
-      </c>
-      <c r="B39" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
-        <v>721</v>
-      </c>
-      <c r="B40" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" s="2" t="s">
-        <v>722</v>
-      </c>
-      <c r="B41" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42" s="2" t="s">
-        <v>723</v>
-      </c>
-      <c r="B42" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43" s="2" t="s">
-        <v>724</v>
-      </c>
-      <c r="B43" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44" s="2" t="s">
-        <v>725</v>
-      </c>
-      <c r="B44" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A45" s="2" t="s">
-        <v>726</v>
-      </c>
-      <c r="B45" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A46" s="2" t="s">
-        <v>727</v>
-      </c>
-      <c r="B46" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A47" s="2" t="s">
-        <v>728</v>
-      </c>
-      <c r="B47" t="s">
-        <v>714</v>
       </c>
     </row>
   </sheetData>
@@ -10584,8 +11652,479 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{867694C3-947A-415D-8A10-3CC2EBC6A1B4}">
+  <dimension ref="A1:C56"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.125" customWidth="1"/>
+    <col min="2" max="2" width="27.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="C2" s="4"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>409</v>
+      </c>
+      <c r="B3" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="B4" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>411</v>
+      </c>
+      <c r="B5" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="B6" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>413</v>
+      </c>
+      <c r="B7" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="B8" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>415</v>
+      </c>
+      <c r="B9" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="B10" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>417</v>
+      </c>
+      <c r="B11" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="B12" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>449</v>
+      </c>
+      <c r="B13" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="B14" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>451</v>
+      </c>
+      <c r="B15" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="B16" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>453</v>
+      </c>
+      <c r="B17" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="B18" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>455</v>
+      </c>
+      <c r="B19" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="B20" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>457</v>
+      </c>
+      <c r="B21" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="B22" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>459</v>
+      </c>
+      <c r="B23" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="B24" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>461</v>
+      </c>
+      <c r="B25" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="B26" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>463</v>
+      </c>
+      <c r="B27" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="B28" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>465</v>
+      </c>
+      <c r="B29" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="B30" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>467</v>
+      </c>
+      <c r="B31" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="B32" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="B33" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="B34" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="B35" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="B36" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="B37" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="B38" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="B39" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="B40" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="B41" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="B42" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="B43" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="B44" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="B45" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="B46" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="B47" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="B48" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="B49" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="B50" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="B51" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="B52" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="B53" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="B54" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="B55" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" s="2" t="s">
+        <v>835</v>
+      </c>
+      <c r="B56" t="s">
+        <v>822</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35C8B6C3-1161-48DB-B39F-D1176282C075}">
-  <dimension ref="A1:H78"/>
+  <dimension ref="A1:H226"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.375" customWidth="1"/>
@@ -12396,12 +13935,3431 @@
         <v>551</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="F78" t="s">
         <v>558</v>
       </c>
       <c r="G78">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A79" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="C79" s="4">
+        <v>1230</v>
+      </c>
+      <c r="D79" t="s">
+        <v>551</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F79" t="s">
+        <v>555</v>
+      </c>
+      <c r="G79">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A80" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B80" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="C80" s="9">
+        <v>2080</v>
+      </c>
+      <c r="D80" t="s">
+        <v>551</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F80" t="s">
+        <v>555</v>
+      </c>
+      <c r="G80">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A81" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B81" s="8" t="s">
+        <v>722</v>
+      </c>
+      <c r="C81" s="9">
+        <v>2285</v>
+      </c>
+      <c r="D81" t="s">
+        <v>551</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F81" t="s">
+        <v>555</v>
+      </c>
+      <c r="G81">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A82" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B82" s="8" t="s">
+        <v>723</v>
+      </c>
+      <c r="C82" s="9">
+        <v>9000</v>
+      </c>
+      <c r="D82" t="s">
+        <v>551</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F82" t="s">
+        <v>555</v>
+      </c>
+      <c r="G82">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A83" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B83" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="C83" s="9">
+        <v>1300</v>
+      </c>
+      <c r="D83" t="s">
+        <v>551</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F83" t="s">
+        <v>555</v>
+      </c>
+      <c r="G83">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A84" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B84" s="8" t="s">
+        <v>722</v>
+      </c>
+      <c r="C84" s="9">
+        <v>1289</v>
+      </c>
+      <c r="D84" t="s">
+        <v>551</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F84" t="s">
+        <v>555</v>
+      </c>
+      <c r="G84">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A85" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B85" s="8" t="s">
+        <v>723</v>
+      </c>
+      <c r="C85" s="9">
+        <v>970</v>
+      </c>
+      <c r="D85" t="s">
+        <v>551</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F85" t="s">
+        <v>555</v>
+      </c>
+      <c r="G85">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A86" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B86" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="C86" s="9">
+        <v>641</v>
+      </c>
+      <c r="D86" t="s">
+        <v>551</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F86" t="s">
+        <v>555</v>
+      </c>
+      <c r="G86">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A87" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B87" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="C87" s="9">
+        <v>235</v>
+      </c>
+      <c r="D87" t="s">
+        <v>551</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F87" t="s">
+        <v>555</v>
+      </c>
+      <c r="G87">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A88" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B88" s="8" t="s">
+        <v>722</v>
+      </c>
+      <c r="C88" s="9">
+        <v>457</v>
+      </c>
+      <c r="D88" t="s">
+        <v>551</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F88" t="s">
+        <v>555</v>
+      </c>
+      <c r="G88">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A89" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B89" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="C89" s="9">
+        <v>630</v>
+      </c>
+      <c r="D89" t="s">
+        <v>551</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F89" t="s">
+        <v>555</v>
+      </c>
+      <c r="G89">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A90" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B90" s="8" t="s">
+        <v>723</v>
+      </c>
+      <c r="C90" s="9">
+        <v>930</v>
+      </c>
+      <c r="D90" t="s">
+        <v>551</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F90" t="s">
+        <v>555</v>
+      </c>
+      <c r="G90">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A91" s="8" t="s">
+        <v>735</v>
+      </c>
+      <c r="B91" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="C91" s="9">
+        <v>112</v>
+      </c>
+      <c r="D91" t="s">
+        <v>551</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F91" t="s">
+        <v>555</v>
+      </c>
+      <c r="G91">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A92" s="8" t="s">
+        <v>735</v>
+      </c>
+      <c r="B92" s="8" t="s">
+        <v>722</v>
+      </c>
+      <c r="C92" s="9">
+        <v>282</v>
+      </c>
+      <c r="D92" t="s">
+        <v>551</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F92" t="s">
+        <v>555</v>
+      </c>
+      <c r="G92">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A93" s="8" t="s">
+        <v>735</v>
+      </c>
+      <c r="B93" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="C93" s="9">
+        <v>110</v>
+      </c>
+      <c r="D93" t="s">
+        <v>551</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F93" t="s">
+        <v>555</v>
+      </c>
+      <c r="G93">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A94" s="8" t="s">
+        <v>735</v>
+      </c>
+      <c r="B94" s="8" t="s">
+        <v>723</v>
+      </c>
+      <c r="C94" s="9">
+        <v>170</v>
+      </c>
+      <c r="D94" t="s">
+        <v>551</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F94" t="s">
+        <v>555</v>
+      </c>
+      <c r="G94">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A95" s="8" t="s">
+        <v>736</v>
+      </c>
+      <c r="B95" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="C95" s="9">
+        <v>79</v>
+      </c>
+      <c r="D95" t="s">
+        <v>551</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F95" t="s">
+        <v>555</v>
+      </c>
+      <c r="G95">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A96" s="8" t="s">
+        <v>736</v>
+      </c>
+      <c r="B96" s="8" t="s">
+        <v>722</v>
+      </c>
+      <c r="C96" s="9">
+        <v>204</v>
+      </c>
+      <c r="D96" t="s">
+        <v>551</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F96" t="s">
+        <v>555</v>
+      </c>
+      <c r="G96">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A97" s="8" t="s">
+        <v>736</v>
+      </c>
+      <c r="B97" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="C97" s="9">
+        <v>60</v>
+      </c>
+      <c r="D97" t="s">
+        <v>551</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F97" t="s">
+        <v>555</v>
+      </c>
+      <c r="G97">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A98" s="8" t="s">
+        <v>736</v>
+      </c>
+      <c r="B98" s="8" t="s">
+        <v>723</v>
+      </c>
+      <c r="C98" s="9">
+        <v>350</v>
+      </c>
+      <c r="D98" t="s">
+        <v>551</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F98" t="s">
+        <v>555</v>
+      </c>
+      <c r="G98">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A99" s="8" t="s">
+        <v>734</v>
+      </c>
+      <c r="B99" s="8" t="s">
+        <v>723</v>
+      </c>
+      <c r="C99" s="9">
+        <v>1350</v>
+      </c>
+      <c r="D99" t="s">
+        <v>551</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F99" t="s">
+        <v>555</v>
+      </c>
+      <c r="G99">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A100" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B100" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="C100" s="9">
+        <v>180</v>
+      </c>
+      <c r="D100" t="s">
+        <v>551</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F100" t="s">
+        <v>555</v>
+      </c>
+      <c r="G100">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A101" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B101" s="8" t="s">
+        <v>466</v>
+      </c>
+      <c r="C101" s="9">
+        <v>337</v>
+      </c>
+      <c r="D101" t="s">
+        <v>551</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F101" t="s">
+        <v>555</v>
+      </c>
+      <c r="G101">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A102" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B102" s="8" t="s">
+        <v>716</v>
+      </c>
+      <c r="C102" s="9">
+        <v>530</v>
+      </c>
+      <c r="D102" t="s">
+        <v>551</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F102" t="s">
+        <v>555</v>
+      </c>
+      <c r="G102">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A103" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B103" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="C103" s="9">
+        <v>600</v>
+      </c>
+      <c r="D103" t="s">
+        <v>551</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F103" t="s">
+        <v>555</v>
+      </c>
+      <c r="G103">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A104" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B104" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="C104" s="9">
+        <v>10</v>
+      </c>
+      <c r="D104" t="s">
+        <v>551</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F104" t="s">
+        <v>555</v>
+      </c>
+      <c r="G104">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A105" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B105" s="8" t="s">
+        <v>466</v>
+      </c>
+      <c r="C105" s="9">
+        <v>425</v>
+      </c>
+      <c r="D105" t="s">
+        <v>551</v>
+      </c>
+      <c r="E105" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F105" t="s">
+        <v>555</v>
+      </c>
+      <c r="G105">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A106" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="B106" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="C106" s="9">
+        <v>630</v>
+      </c>
+      <c r="D106" t="s">
+        <v>551</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F106" t="s">
+        <v>555</v>
+      </c>
+      <c r="G106">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A107" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="B107" s="8" t="s">
+        <v>723</v>
+      </c>
+      <c r="C107" s="9">
+        <v>500</v>
+      </c>
+      <c r="D107" t="s">
+        <v>551</v>
+      </c>
+      <c r="E107" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F107" t="s">
+        <v>555</v>
+      </c>
+      <c r="G107">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A108" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="B108" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="C108" s="9">
+        <v>360</v>
+      </c>
+      <c r="D108" t="s">
+        <v>551</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F108" t="s">
+        <v>555</v>
+      </c>
+      <c r="G108">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A109" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="B109" s="8" t="s">
+        <v>716</v>
+      </c>
+      <c r="C109" s="9">
+        <v>180</v>
+      </c>
+      <c r="D109" t="s">
+        <v>551</v>
+      </c>
+      <c r="E109" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F109" t="s">
+        <v>555</v>
+      </c>
+      <c r="G109">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A110" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B110" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="C110" s="9">
+        <v>810</v>
+      </c>
+      <c r="D110" t="s">
+        <v>551</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F110" t="s">
+        <v>555</v>
+      </c>
+      <c r="G110">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A111" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B111" s="8" t="s">
+        <v>466</v>
+      </c>
+      <c r="C111" s="9">
+        <v>1586</v>
+      </c>
+      <c r="D111" t="s">
+        <v>551</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F111" t="s">
+        <v>555</v>
+      </c>
+      <c r="G111">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A112" s="8" t="s">
+        <v>841</v>
+      </c>
+      <c r="B112" s="8" t="s">
+        <v>714</v>
+      </c>
+      <c r="C112" s="9">
+        <v>310</v>
+      </c>
+      <c r="D112" t="s">
+        <v>551</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F112" t="s">
+        <v>555</v>
+      </c>
+      <c r="G112">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A113" s="8" t="s">
+        <v>841</v>
+      </c>
+      <c r="B113" s="8" t="s">
+        <v>717</v>
+      </c>
+      <c r="C113" s="9">
+        <v>96</v>
+      </c>
+      <c r="D113" t="s">
+        <v>551</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F113" t="s">
+        <v>555</v>
+      </c>
+      <c r="G113">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A114" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B114" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="C114" s="9">
+        <v>600</v>
+      </c>
+      <c r="D114" t="s">
+        <v>551</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F114" t="s">
+        <v>555</v>
+      </c>
+      <c r="G114">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A115" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B115" s="8" t="s">
+        <v>723</v>
+      </c>
+      <c r="C115" s="9">
+        <v>180</v>
+      </c>
+      <c r="D115" t="s">
+        <v>551</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F115" t="s">
+        <v>555</v>
+      </c>
+      <c r="G115">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A116" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B116" s="8" t="s">
+        <v>724</v>
+      </c>
+      <c r="C116" s="9">
+        <v>730</v>
+      </c>
+      <c r="D116" t="s">
+        <v>551</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F116" t="s">
+        <v>555</v>
+      </c>
+      <c r="G116">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A117" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B117" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="C117" s="9">
+        <v>125</v>
+      </c>
+      <c r="D117" t="s">
+        <v>551</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F117" t="s">
+        <v>555</v>
+      </c>
+      <c r="G117">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A118" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B118" s="8" t="s">
+        <v>466</v>
+      </c>
+      <c r="C118" s="9">
+        <v>152</v>
+      </c>
+      <c r="D118" t="s">
+        <v>551</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F118" t="s">
+        <v>555</v>
+      </c>
+      <c r="G118">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A119" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B119" s="8" t="s">
+        <v>466</v>
+      </c>
+      <c r="C119" s="9">
+        <v>12</v>
+      </c>
+      <c r="D119" t="s">
+        <v>551</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F119" t="s">
+        <v>555</v>
+      </c>
+      <c r="G119">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A120" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="B120" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="C120" s="9">
+        <v>205</v>
+      </c>
+      <c r="D120" t="s">
+        <v>551</v>
+      </c>
+      <c r="E120" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F120" t="s">
+        <v>555</v>
+      </c>
+      <c r="G120">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A121" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B121" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="C121" s="9">
+        <v>649</v>
+      </c>
+      <c r="D121" t="s">
+        <v>551</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F121" t="s">
+        <v>555</v>
+      </c>
+      <c r="G121">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A122" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B122" s="8" t="s">
+        <v>722</v>
+      </c>
+      <c r="C122" s="9">
+        <v>378</v>
+      </c>
+      <c r="D122" t="s">
+        <v>551</v>
+      </c>
+      <c r="E122" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F122" t="s">
+        <v>555</v>
+      </c>
+      <c r="G122">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A123" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B123" s="8" t="s">
+        <v>406</v>
+      </c>
+      <c r="C123" s="9">
+        <v>147</v>
+      </c>
+      <c r="D123" t="s">
+        <v>551</v>
+      </c>
+      <c r="E123" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F123" t="s">
+        <v>555</v>
+      </c>
+      <c r="G123">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A124" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B124" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="C124" s="9">
+        <v>306</v>
+      </c>
+      <c r="D124" t="s">
+        <v>551</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F124" t="s">
+        <v>555</v>
+      </c>
+      <c r="G124">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A125" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B125" s="8" t="s">
+        <v>725</v>
+      </c>
+      <c r="C125" s="9">
+        <v>130</v>
+      </c>
+      <c r="D125" t="s">
+        <v>551</v>
+      </c>
+      <c r="E125" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F125" t="s">
+        <v>555</v>
+      </c>
+      <c r="G125">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A126" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B126" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="C126" s="9">
+        <v>160</v>
+      </c>
+      <c r="D126" t="s">
+        <v>551</v>
+      </c>
+      <c r="E126" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F126" t="s">
+        <v>555</v>
+      </c>
+      <c r="G126">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A127" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="B127" s="8" t="s">
+        <v>722</v>
+      </c>
+      <c r="C127" s="9">
+        <v>351</v>
+      </c>
+      <c r="D127" t="s">
+        <v>551</v>
+      </c>
+      <c r="E127" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F127" t="s">
+        <v>555</v>
+      </c>
+      <c r="G127">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A128" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="B128" s="8" t="s">
+        <v>715</v>
+      </c>
+      <c r="C128" s="9">
+        <v>680</v>
+      </c>
+      <c r="D128" t="s">
+        <v>551</v>
+      </c>
+      <c r="E128" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F128" t="s">
+        <v>555</v>
+      </c>
+      <c r="G128">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A129" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="B129" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="C129" s="9">
+        <v>350</v>
+      </c>
+      <c r="D129" t="s">
+        <v>551</v>
+      </c>
+      <c r="E129" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F129" t="s">
+        <v>555</v>
+      </c>
+      <c r="G129">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A130" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="B130" s="8" t="s">
+        <v>715</v>
+      </c>
+      <c r="C130" s="9">
+        <v>420</v>
+      </c>
+      <c r="D130" t="s">
+        <v>551</v>
+      </c>
+      <c r="E130" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F130" t="s">
+        <v>555</v>
+      </c>
+      <c r="G130">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A131" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="B131" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="C131" s="9">
+        <v>210</v>
+      </c>
+      <c r="D131" t="s">
+        <v>551</v>
+      </c>
+      <c r="E131" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F131" t="s">
+        <v>555</v>
+      </c>
+      <c r="G131">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A132" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B132" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="C132" s="9">
+        <v>720</v>
+      </c>
+      <c r="D132" t="s">
+        <v>551</v>
+      </c>
+      <c r="E132" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F132" t="s">
+        <v>555</v>
+      </c>
+      <c r="G132">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A133" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B133" s="8" t="s">
+        <v>466</v>
+      </c>
+      <c r="C133" s="9">
+        <v>583</v>
+      </c>
+      <c r="D133" t="s">
+        <v>551</v>
+      </c>
+      <c r="E133" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F133" t="s">
+        <v>555</v>
+      </c>
+      <c r="G133">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A134" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B134" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="C134" s="9">
+        <v>450</v>
+      </c>
+      <c r="D134" t="s">
+        <v>551</v>
+      </c>
+      <c r="E134" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F134" t="s">
+        <v>555</v>
+      </c>
+      <c r="G134">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A135" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B135" s="8" t="s">
+        <v>466</v>
+      </c>
+      <c r="C135" s="9">
+        <v>480</v>
+      </c>
+      <c r="D135" t="s">
+        <v>551</v>
+      </c>
+      <c r="E135" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F135" t="s">
+        <v>555</v>
+      </c>
+      <c r="G135">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A136" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B136" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="C136" s="9">
+        <v>400</v>
+      </c>
+      <c r="D136" t="s">
+        <v>551</v>
+      </c>
+      <c r="E136" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F136" t="s">
+        <v>555</v>
+      </c>
+      <c r="G136">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A137" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B137" s="8" t="s">
+        <v>406</v>
+      </c>
+      <c r="C137" s="9">
+        <v>275</v>
+      </c>
+      <c r="D137" t="s">
+        <v>551</v>
+      </c>
+      <c r="E137" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F137" t="s">
+        <v>555</v>
+      </c>
+      <c r="G137">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A138" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B138" s="8" t="s">
+        <v>406</v>
+      </c>
+      <c r="C138" s="9">
+        <v>123</v>
+      </c>
+      <c r="D138" t="s">
+        <v>551</v>
+      </c>
+      <c r="E138" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F138" t="s">
+        <v>555</v>
+      </c>
+      <c r="G138">
+        <v>2025</v>
+      </c>
+      <c r="H138" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A139" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B139" s="8" t="s">
+        <v>717</v>
+      </c>
+      <c r="C139" s="9">
+        <v>100</v>
+      </c>
+      <c r="D139" t="s">
+        <v>551</v>
+      </c>
+      <c r="E139" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F139" t="s">
+        <v>555</v>
+      </c>
+      <c r="G139">
+        <v>2025</v>
+      </c>
+      <c r="H139" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A140" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="B140" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="C140" s="9">
+        <v>20</v>
+      </c>
+      <c r="D140" t="s">
+        <v>551</v>
+      </c>
+      <c r="E140" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F140" t="s">
+        <v>555</v>
+      </c>
+      <c r="G140">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A141" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="B141" s="8" t="s">
+        <v>722</v>
+      </c>
+      <c r="C141" s="9">
+        <v>170</v>
+      </c>
+      <c r="D141" t="s">
+        <v>551</v>
+      </c>
+      <c r="E141" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F141" t="s">
+        <v>555</v>
+      </c>
+      <c r="G141">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A142" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="B142" s="8" t="s">
+        <v>720</v>
+      </c>
+      <c r="C142" s="9">
+        <v>275</v>
+      </c>
+      <c r="D142" t="s">
+        <v>551</v>
+      </c>
+      <c r="E142" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F142" t="s">
+        <v>555</v>
+      </c>
+      <c r="G142">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A143" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="B143" s="8" t="s">
+        <v>723</v>
+      </c>
+      <c r="C143" s="9">
+        <v>150</v>
+      </c>
+      <c r="D143" t="s">
+        <v>551</v>
+      </c>
+      <c r="E143" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F143" t="s">
+        <v>555</v>
+      </c>
+      <c r="G143">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A144" s="8" t="s">
+        <v>737</v>
+      </c>
+      <c r="B144" s="8" t="s">
+        <v>718</v>
+      </c>
+      <c r="C144" s="9">
+        <v>97</v>
+      </c>
+      <c r="D144" t="s">
+        <v>551</v>
+      </c>
+      <c r="E144" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F144" t="s">
+        <v>555</v>
+      </c>
+      <c r="G144">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A145" s="8" t="s">
+        <v>737</v>
+      </c>
+      <c r="B145" s="8" t="s">
+        <v>720</v>
+      </c>
+      <c r="C145" s="9">
+        <v>260</v>
+      </c>
+      <c r="D145" t="s">
+        <v>551</v>
+      </c>
+      <c r="E145" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F145" t="s">
+        <v>555</v>
+      </c>
+      <c r="G145">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A146" s="8" t="s">
+        <v>737</v>
+      </c>
+      <c r="B146" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="C146" s="9">
+        <v>50</v>
+      </c>
+      <c r="D146" t="s">
+        <v>551</v>
+      </c>
+      <c r="E146" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F146" t="s">
+        <v>555</v>
+      </c>
+      <c r="G146">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A147" s="8" t="s">
+        <v>738</v>
+      </c>
+      <c r="B147" s="8" t="s">
+        <v>718</v>
+      </c>
+      <c r="C147" s="9">
+        <v>110</v>
+      </c>
+      <c r="D147" t="s">
+        <v>551</v>
+      </c>
+      <c r="E147" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F147" t="s">
+        <v>555</v>
+      </c>
+      <c r="G147">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A148" s="8" t="s">
+        <v>738</v>
+      </c>
+      <c r="B148" s="8" t="s">
+        <v>720</v>
+      </c>
+      <c r="C148" s="9">
+        <v>120</v>
+      </c>
+      <c r="D148" t="s">
+        <v>551</v>
+      </c>
+      <c r="E148" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F148" t="s">
+        <v>555</v>
+      </c>
+      <c r="G148">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A149" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="B149" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="C149" s="9">
+        <v>90</v>
+      </c>
+      <c r="D149" t="s">
+        <v>551</v>
+      </c>
+      <c r="E149" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F149" t="s">
+        <v>555</v>
+      </c>
+      <c r="G149">
+        <v>2025</v>
+      </c>
+      <c r="H149" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A150" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B150" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="C150" s="9">
+        <v>757</v>
+      </c>
+      <c r="D150" t="s">
+        <v>551</v>
+      </c>
+      <c r="E150" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F150" t="s">
+        <v>555</v>
+      </c>
+      <c r="G150">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A151" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B151" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="C151" s="9">
+        <v>1030</v>
+      </c>
+      <c r="D151" t="s">
+        <v>551</v>
+      </c>
+      <c r="E151" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F151" t="s">
+        <v>555</v>
+      </c>
+      <c r="G151">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A152" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="B152" s="8" t="s">
+        <v>715</v>
+      </c>
+      <c r="C152" s="9">
+        <v>450</v>
+      </c>
+      <c r="D152" t="s">
+        <v>551</v>
+      </c>
+      <c r="E152" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F152" t="s">
+        <v>555</v>
+      </c>
+      <c r="G152">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A153" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="B153" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="C153" s="9">
+        <v>330</v>
+      </c>
+      <c r="D153" t="s">
+        <v>551</v>
+      </c>
+      <c r="E153" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F153" t="s">
+        <v>555</v>
+      </c>
+      <c r="G153">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A154" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="B154" s="8" t="s">
+        <v>715</v>
+      </c>
+      <c r="C154" s="9">
+        <v>338</v>
+      </c>
+      <c r="D154" t="s">
+        <v>551</v>
+      </c>
+      <c r="E154" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F154" t="s">
+        <v>555</v>
+      </c>
+      <c r="G154">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A155" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="B155" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="C155" s="9">
+        <v>480</v>
+      </c>
+      <c r="D155" t="s">
+        <v>551</v>
+      </c>
+      <c r="E155" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F155" t="s">
+        <v>555</v>
+      </c>
+      <c r="G155">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A156" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="B156" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="C156" s="9">
+        <v>170</v>
+      </c>
+      <c r="D156" t="s">
+        <v>551</v>
+      </c>
+      <c r="E156" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F156" t="s">
+        <v>555</v>
+      </c>
+      <c r="G156">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A157" s="8" t="s">
+        <v>739</v>
+      </c>
+      <c r="B157" s="8" t="s">
+        <v>726</v>
+      </c>
+      <c r="C157" s="9">
+        <v>30</v>
+      </c>
+      <c r="D157" t="s">
+        <v>551</v>
+      </c>
+      <c r="E157" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F157" t="s">
+        <v>555</v>
+      </c>
+      <c r="G157">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A158" s="8" t="s">
+        <v>739</v>
+      </c>
+      <c r="B158" s="8" t="s">
+        <v>462</v>
+      </c>
+      <c r="C158" s="9">
+        <v>250</v>
+      </c>
+      <c r="D158" t="s">
+        <v>551</v>
+      </c>
+      <c r="E158" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F158" t="s">
+        <v>555</v>
+      </c>
+      <c r="G158">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A159" s="8" t="s">
+        <v>739</v>
+      </c>
+      <c r="B159" s="8" t="s">
+        <v>713</v>
+      </c>
+      <c r="C159" s="9">
+        <v>610</v>
+      </c>
+      <c r="D159" t="s">
+        <v>551</v>
+      </c>
+      <c r="E159" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F159" t="s">
+        <v>555</v>
+      </c>
+      <c r="G159">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A160" s="8" t="s">
+        <v>740</v>
+      </c>
+      <c r="B160" s="8" t="s">
+        <v>462</v>
+      </c>
+      <c r="C160" s="9">
+        <v>160</v>
+      </c>
+      <c r="D160" t="s">
+        <v>551</v>
+      </c>
+      <c r="E160" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F160" t="s">
+        <v>555</v>
+      </c>
+      <c r="G160">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A161" s="8" t="s">
+        <v>740</v>
+      </c>
+      <c r="B161" s="8" t="s">
+        <v>466</v>
+      </c>
+      <c r="C161" s="9">
+        <v>150</v>
+      </c>
+      <c r="D161" t="s">
+        <v>551</v>
+      </c>
+      <c r="E161" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F161" t="s">
+        <v>555</v>
+      </c>
+      <c r="G161">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A162" s="8" t="s">
+        <v>686</v>
+      </c>
+      <c r="B162" s="8" t="s">
+        <v>719</v>
+      </c>
+      <c r="C162" s="9">
+        <v>1500</v>
+      </c>
+      <c r="D162" t="s">
+        <v>551</v>
+      </c>
+      <c r="E162" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="F162" t="s">
+        <v>555</v>
+      </c>
+      <c r="G162">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A163" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B163" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="C163" s="4">
+        <v>1100</v>
+      </c>
+      <c r="D163" t="s">
+        <v>551</v>
+      </c>
+      <c r="E163" t="s">
+        <v>817</v>
+      </c>
+      <c r="F163" t="s">
+        <v>555</v>
+      </c>
+      <c r="G163">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A164" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B164" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="C164" s="9">
+        <v>1300</v>
+      </c>
+      <c r="D164" t="s">
+        <v>551</v>
+      </c>
+      <c r="E164" t="s">
+        <v>817</v>
+      </c>
+      <c r="F164" t="s">
+        <v>555</v>
+      </c>
+      <c r="G164">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A165" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B165" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="C165" s="9">
+        <v>1525</v>
+      </c>
+      <c r="D165" t="s">
+        <v>551</v>
+      </c>
+      <c r="E165" t="s">
+        <v>817</v>
+      </c>
+      <c r="F165" t="s">
+        <v>555</v>
+      </c>
+      <c r="G165">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A166" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B166" s="8" t="s">
+        <v>805</v>
+      </c>
+      <c r="C166" s="9">
+        <v>850</v>
+      </c>
+      <c r="D166" t="s">
+        <v>551</v>
+      </c>
+      <c r="E166" t="s">
+        <v>817</v>
+      </c>
+      <c r="F166" t="s">
+        <v>555</v>
+      </c>
+      <c r="G166">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A167" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B167" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="C167" s="9">
+        <v>550</v>
+      </c>
+      <c r="D167" t="s">
+        <v>551</v>
+      </c>
+      <c r="E167" t="s">
+        <v>817</v>
+      </c>
+      <c r="F167" t="s">
+        <v>555</v>
+      </c>
+      <c r="G167">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A168" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B168" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="C168" s="9">
+        <v>1064</v>
+      </c>
+      <c r="D168" t="s">
+        <v>551</v>
+      </c>
+      <c r="E168" t="s">
+        <v>817</v>
+      </c>
+      <c r="F168" t="s">
+        <v>555</v>
+      </c>
+      <c r="G168">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A169" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B169" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="C169" s="9">
+        <v>680</v>
+      </c>
+      <c r="D169" t="s">
+        <v>551</v>
+      </c>
+      <c r="E169" t="s">
+        <v>817</v>
+      </c>
+      <c r="F169" t="s">
+        <v>555</v>
+      </c>
+      <c r="G169">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A170" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B170" s="8" t="s">
+        <v>816</v>
+      </c>
+      <c r="C170" s="9">
+        <v>420</v>
+      </c>
+      <c r="D170" t="s">
+        <v>551</v>
+      </c>
+      <c r="E170" t="s">
+        <v>817</v>
+      </c>
+      <c r="F170" t="s">
+        <v>555</v>
+      </c>
+      <c r="G170">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A171" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B171" s="8" t="s">
+        <v>805</v>
+      </c>
+      <c r="C171" s="9">
+        <v>451</v>
+      </c>
+      <c r="D171" t="s">
+        <v>551</v>
+      </c>
+      <c r="E171" t="s">
+        <v>817</v>
+      </c>
+      <c r="F171" t="s">
+        <v>555</v>
+      </c>
+      <c r="G171">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A172" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B172" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="C172" s="9">
+        <v>240</v>
+      </c>
+      <c r="D172" t="s">
+        <v>551</v>
+      </c>
+      <c r="E172" t="s">
+        <v>817</v>
+      </c>
+      <c r="F172" t="s">
+        <v>555</v>
+      </c>
+      <c r="G172">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A173" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B173" s="8" t="s">
+        <v>805</v>
+      </c>
+      <c r="C173" s="9">
+        <v>410</v>
+      </c>
+      <c r="D173" t="s">
+        <v>551</v>
+      </c>
+      <c r="E173" t="s">
+        <v>817</v>
+      </c>
+      <c r="F173" t="s">
+        <v>555</v>
+      </c>
+      <c r="G173">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A174" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B174" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="C174" s="9">
+        <v>270</v>
+      </c>
+      <c r="D174" t="s">
+        <v>551</v>
+      </c>
+      <c r="E174" t="s">
+        <v>817</v>
+      </c>
+      <c r="F174" t="s">
+        <v>555</v>
+      </c>
+      <c r="G174">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A175" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B175" s="8" t="s">
+        <v>816</v>
+      </c>
+      <c r="C175" s="9">
+        <v>338</v>
+      </c>
+      <c r="D175" t="s">
+        <v>551</v>
+      </c>
+      <c r="E175" t="s">
+        <v>817</v>
+      </c>
+      <c r="F175" t="s">
+        <v>555</v>
+      </c>
+      <c r="G175">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A176" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B176" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="C176" s="9">
+        <v>1267</v>
+      </c>
+      <c r="D176" t="s">
+        <v>551</v>
+      </c>
+      <c r="E176" t="s">
+        <v>817</v>
+      </c>
+      <c r="F176" t="s">
+        <v>555</v>
+      </c>
+      <c r="G176">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A177" s="8" t="s">
+        <v>735</v>
+      </c>
+      <c r="B177" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="C177" s="9">
+        <v>120</v>
+      </c>
+      <c r="D177" t="s">
+        <v>551</v>
+      </c>
+      <c r="E177" t="s">
+        <v>817</v>
+      </c>
+      <c r="F177" t="s">
+        <v>555</v>
+      </c>
+      <c r="G177">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A178" s="8" t="s">
+        <v>735</v>
+      </c>
+      <c r="B178" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="C178" s="9">
+        <v>100</v>
+      </c>
+      <c r="D178" t="s">
+        <v>551</v>
+      </c>
+      <c r="E178" t="s">
+        <v>817</v>
+      </c>
+      <c r="F178" t="s">
+        <v>555</v>
+      </c>
+      <c r="G178">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A179" s="8" t="s">
+        <v>736</v>
+      </c>
+      <c r="B179" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="C179" s="9">
+        <v>60</v>
+      </c>
+      <c r="D179" t="s">
+        <v>551</v>
+      </c>
+      <c r="E179" t="s">
+        <v>817</v>
+      </c>
+      <c r="F179" t="s">
+        <v>555</v>
+      </c>
+      <c r="G179">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A180" s="8" t="s">
+        <v>736</v>
+      </c>
+      <c r="B180" s="8" t="s">
+        <v>805</v>
+      </c>
+      <c r="C180" s="9">
+        <v>1350</v>
+      </c>
+      <c r="D180" t="s">
+        <v>551</v>
+      </c>
+      <c r="E180" t="s">
+        <v>817</v>
+      </c>
+      <c r="F180" t="s">
+        <v>555</v>
+      </c>
+      <c r="G180">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A181" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B181" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="C181" s="9">
+        <v>135</v>
+      </c>
+      <c r="D181" t="s">
+        <v>551</v>
+      </c>
+      <c r="E181" t="s">
+        <v>817</v>
+      </c>
+      <c r="F181" t="s">
+        <v>555</v>
+      </c>
+      <c r="G181">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A182" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B182" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="C182" s="9">
+        <v>435</v>
+      </c>
+      <c r="D182" t="s">
+        <v>551</v>
+      </c>
+      <c r="E182" t="s">
+        <v>817</v>
+      </c>
+      <c r="F182" t="s">
+        <v>555</v>
+      </c>
+      <c r="G182">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A183" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B183" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="C183" s="9">
+        <v>280</v>
+      </c>
+      <c r="D183" t="s">
+        <v>551</v>
+      </c>
+      <c r="E183" t="s">
+        <v>817</v>
+      </c>
+      <c r="F183" t="s">
+        <v>555</v>
+      </c>
+      <c r="G183">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A184" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B184" s="8" t="s">
+        <v>805</v>
+      </c>
+      <c r="C184" s="9">
+        <v>300</v>
+      </c>
+      <c r="D184" t="s">
+        <v>551</v>
+      </c>
+      <c r="E184" t="s">
+        <v>817</v>
+      </c>
+      <c r="F184" t="s">
+        <v>555</v>
+      </c>
+      <c r="G184">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A185" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B185" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="C185" s="9">
+        <v>300</v>
+      </c>
+      <c r="D185" t="s">
+        <v>551</v>
+      </c>
+      <c r="E185" t="s">
+        <v>817</v>
+      </c>
+      <c r="F185" t="s">
+        <v>555</v>
+      </c>
+      <c r="G185">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A186" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B186" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="C186" s="9">
+        <v>125</v>
+      </c>
+      <c r="D186" t="s">
+        <v>551</v>
+      </c>
+      <c r="E186" t="s">
+        <v>817</v>
+      </c>
+      <c r="F186" t="s">
+        <v>555</v>
+      </c>
+      <c r="G186">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A187" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B187" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="C187" s="9">
+        <v>500</v>
+      </c>
+      <c r="D187" t="s">
+        <v>551</v>
+      </c>
+      <c r="E187" t="s">
+        <v>817</v>
+      </c>
+      <c r="F187" t="s">
+        <v>555</v>
+      </c>
+      <c r="G187">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A188" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="B188" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="C188" s="9">
+        <v>575</v>
+      </c>
+      <c r="D188" t="s">
+        <v>551</v>
+      </c>
+      <c r="E188" t="s">
+        <v>817</v>
+      </c>
+      <c r="F188" t="s">
+        <v>555</v>
+      </c>
+      <c r="G188">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A189" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="B189" s="8" t="s">
+        <v>805</v>
+      </c>
+      <c r="C189" s="9">
+        <v>550</v>
+      </c>
+      <c r="D189" t="s">
+        <v>551</v>
+      </c>
+      <c r="E189" t="s">
+        <v>817</v>
+      </c>
+      <c r="F189" t="s">
+        <v>555</v>
+      </c>
+      <c r="G189">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A190" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B190" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="C190" s="9">
+        <v>230</v>
+      </c>
+      <c r="D190" t="s">
+        <v>551</v>
+      </c>
+      <c r="E190" t="s">
+        <v>817</v>
+      </c>
+      <c r="F190" t="s">
+        <v>555</v>
+      </c>
+      <c r="G190">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A191" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B191" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="C191" s="9">
+        <v>490</v>
+      </c>
+      <c r="D191" t="s">
+        <v>551</v>
+      </c>
+      <c r="E191" t="s">
+        <v>817</v>
+      </c>
+      <c r="F191" t="s">
+        <v>555</v>
+      </c>
+      <c r="G191">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A192" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B192" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="C192" s="9">
+        <v>1117</v>
+      </c>
+      <c r="D192" t="s">
+        <v>551</v>
+      </c>
+      <c r="E192" t="s">
+        <v>817</v>
+      </c>
+      <c r="F192" t="s">
+        <v>555</v>
+      </c>
+      <c r="G192">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A193" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B193" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="C193" s="9">
+        <v>380</v>
+      </c>
+      <c r="D193" t="s">
+        <v>551</v>
+      </c>
+      <c r="E193" t="s">
+        <v>817</v>
+      </c>
+      <c r="F193" t="s">
+        <v>555</v>
+      </c>
+      <c r="G193">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A194" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B194" s="8" t="s">
+        <v>805</v>
+      </c>
+      <c r="C194" s="9">
+        <v>500</v>
+      </c>
+      <c r="D194" t="s">
+        <v>551</v>
+      </c>
+      <c r="E194" t="s">
+        <v>817</v>
+      </c>
+      <c r="F194" t="s">
+        <v>555</v>
+      </c>
+      <c r="G194">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A195" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B195" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="C195" s="9">
+        <v>190</v>
+      </c>
+      <c r="D195" t="s">
+        <v>551</v>
+      </c>
+      <c r="E195" t="s">
+        <v>817</v>
+      </c>
+      <c r="F195" t="s">
+        <v>555</v>
+      </c>
+      <c r="G195">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A196" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B196" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="C196" s="9">
+        <v>150</v>
+      </c>
+      <c r="D196" t="s">
+        <v>551</v>
+      </c>
+      <c r="E196" t="s">
+        <v>817</v>
+      </c>
+      <c r="F196" t="s">
+        <v>555</v>
+      </c>
+      <c r="G196">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A197" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B197" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="C197" s="9">
+        <v>200</v>
+      </c>
+      <c r="D197" t="s">
+        <v>551</v>
+      </c>
+      <c r="E197" t="s">
+        <v>817</v>
+      </c>
+      <c r="F197" t="s">
+        <v>555</v>
+      </c>
+      <c r="G197">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A198" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B198" s="8" t="s">
+        <v>805</v>
+      </c>
+      <c r="C198" s="9">
+        <v>163</v>
+      </c>
+      <c r="D198" t="s">
+        <v>551</v>
+      </c>
+      <c r="E198" t="s">
+        <v>817</v>
+      </c>
+      <c r="F198" t="s">
+        <v>555</v>
+      </c>
+      <c r="G198">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A199" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="B199" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="C199" s="9">
+        <v>577</v>
+      </c>
+      <c r="D199" t="s">
+        <v>551</v>
+      </c>
+      <c r="E199" t="s">
+        <v>817</v>
+      </c>
+      <c r="F199" t="s">
+        <v>555</v>
+      </c>
+      <c r="G199">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A200" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="B200" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="C200" s="9">
+        <v>1071</v>
+      </c>
+      <c r="D200" t="s">
+        <v>551</v>
+      </c>
+      <c r="E200" t="s">
+        <v>817</v>
+      </c>
+      <c r="F200" t="s">
+        <v>555</v>
+      </c>
+      <c r="G200">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A201" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="B201" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="C201" s="9">
+        <v>360</v>
+      </c>
+      <c r="D201" t="s">
+        <v>551</v>
+      </c>
+      <c r="E201" t="s">
+        <v>817</v>
+      </c>
+      <c r="F201" t="s">
+        <v>555</v>
+      </c>
+      <c r="G201">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A202" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="B202" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="C202" s="9">
+        <v>225</v>
+      </c>
+      <c r="D202" t="s">
+        <v>551</v>
+      </c>
+      <c r="E202" t="s">
+        <v>817</v>
+      </c>
+      <c r="F202" t="s">
+        <v>555</v>
+      </c>
+      <c r="G202">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A203" s="8" t="s">
+        <v>734</v>
+      </c>
+      <c r="B203" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="C203" s="9">
+        <v>2000</v>
+      </c>
+      <c r="D203" t="s">
+        <v>551</v>
+      </c>
+      <c r="E203" t="s">
+        <v>817</v>
+      </c>
+      <c r="F203" t="s">
+        <v>555</v>
+      </c>
+      <c r="G203">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A204" s="8" t="s">
+        <v>734</v>
+      </c>
+      <c r="B204" s="8" t="s">
+        <v>816</v>
+      </c>
+      <c r="C204" s="9">
+        <v>1460</v>
+      </c>
+      <c r="D204" t="s">
+        <v>551</v>
+      </c>
+      <c r="E204" t="s">
+        <v>817</v>
+      </c>
+      <c r="F204" t="s">
+        <v>555</v>
+      </c>
+      <c r="G204">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A205" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B205" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="C205" s="9">
+        <v>240</v>
+      </c>
+      <c r="D205" t="s">
+        <v>551</v>
+      </c>
+      <c r="E205" t="s">
+        <v>817</v>
+      </c>
+      <c r="F205" t="s">
+        <v>555</v>
+      </c>
+      <c r="G205">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A206" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B206" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="C206" s="9">
+        <v>730</v>
+      </c>
+      <c r="D206" t="s">
+        <v>551</v>
+      </c>
+      <c r="E206" t="s">
+        <v>817</v>
+      </c>
+      <c r="F206" t="s">
+        <v>555</v>
+      </c>
+      <c r="G206">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A207" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B207" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="C207" s="9">
+        <v>218</v>
+      </c>
+      <c r="D207" t="s">
+        <v>551</v>
+      </c>
+      <c r="E207" t="s">
+        <v>817</v>
+      </c>
+      <c r="F207" t="s">
+        <v>555</v>
+      </c>
+      <c r="G207">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A208" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B208" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="C208" s="9">
+        <v>220</v>
+      </c>
+      <c r="D208" t="s">
+        <v>551</v>
+      </c>
+      <c r="E208" t="s">
+        <v>817</v>
+      </c>
+      <c r="F208" t="s">
+        <v>555</v>
+      </c>
+      <c r="G208">
+        <v>2025</v>
+      </c>
+      <c r="H208" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A209" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B209" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="C209" s="9">
+        <v>80</v>
+      </c>
+      <c r="D209" t="s">
+        <v>551</v>
+      </c>
+      <c r="E209" t="s">
+        <v>817</v>
+      </c>
+      <c r="F209" t="s">
+        <v>555</v>
+      </c>
+      <c r="G209">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A210" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B210" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="C210" s="9">
+        <v>65</v>
+      </c>
+      <c r="D210" t="s">
+        <v>551</v>
+      </c>
+      <c r="E210" t="s">
+        <v>817</v>
+      </c>
+      <c r="F210" t="s">
+        <v>555</v>
+      </c>
+      <c r="G210">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A211" s="8" t="s">
+        <v>737</v>
+      </c>
+      <c r="B211" s="8" t="s">
+        <v>718</v>
+      </c>
+      <c r="C211" s="9">
+        <v>90</v>
+      </c>
+      <c r="D211" t="s">
+        <v>551</v>
+      </c>
+      <c r="E211" t="s">
+        <v>817</v>
+      </c>
+      <c r="F211" t="s">
+        <v>555</v>
+      </c>
+      <c r="G211">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A212" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="B212" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="C212" s="9">
+        <v>220</v>
+      </c>
+      <c r="D212" t="s">
+        <v>551</v>
+      </c>
+      <c r="E212" t="s">
+        <v>817</v>
+      </c>
+      <c r="F212" t="s">
+        <v>555</v>
+      </c>
+      <c r="G212">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A213" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="B213" s="8" t="s">
+        <v>816</v>
+      </c>
+      <c r="C213" s="9">
+        <v>200</v>
+      </c>
+      <c r="D213" t="s">
+        <v>551</v>
+      </c>
+      <c r="E213" t="s">
+        <v>817</v>
+      </c>
+      <c r="F213" t="s">
+        <v>555</v>
+      </c>
+      <c r="G213">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A214" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="B214" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="C214" s="9">
+        <v>165</v>
+      </c>
+      <c r="D214" t="s">
+        <v>551</v>
+      </c>
+      <c r="E214" t="s">
+        <v>817</v>
+      </c>
+      <c r="F214" t="s">
+        <v>555</v>
+      </c>
+      <c r="G214">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A215" s="8" t="s">
+        <v>686</v>
+      </c>
+      <c r="B215" s="8" t="s">
+        <v>467</v>
+      </c>
+      <c r="C215" s="9">
+        <v>700</v>
+      </c>
+      <c r="D215" t="s">
+        <v>551</v>
+      </c>
+      <c r="E215" t="s">
+        <v>817</v>
+      </c>
+      <c r="F215" t="s">
+        <v>555</v>
+      </c>
+      <c r="G215">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A216" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B216" s="3" t="s">
+        <v>830</v>
+      </c>
+      <c r="C216" s="4">
+        <v>200</v>
+      </c>
+      <c r="D216" t="s">
+        <v>551</v>
+      </c>
+      <c r="E216" t="s">
+        <v>819</v>
+      </c>
+      <c r="F216" t="s">
+        <v>555</v>
+      </c>
+      <c r="G216">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A217" s="8" t="s">
+        <v>735</v>
+      </c>
+      <c r="B217" s="8" t="s">
+        <v>830</v>
+      </c>
+      <c r="C217" s="9">
+        <v>40</v>
+      </c>
+      <c r="D217" t="s">
+        <v>551</v>
+      </c>
+      <c r="E217" t="s">
+        <v>819</v>
+      </c>
+      <c r="F217" t="s">
+        <v>555</v>
+      </c>
+      <c r="G217">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A218" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="B218" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C218" s="9">
+        <v>52</v>
+      </c>
+      <c r="D218" t="s">
+        <v>551</v>
+      </c>
+      <c r="E218" t="s">
+        <v>820</v>
+      </c>
+      <c r="F218" t="s">
+        <v>555</v>
+      </c>
+      <c r="G218">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A219" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="B219" s="8" t="s">
+        <v>835</v>
+      </c>
+      <c r="C219" s="9">
+        <v>100</v>
+      </c>
+      <c r="D219" t="s">
+        <v>551</v>
+      </c>
+      <c r="E219" t="s">
+        <v>821</v>
+      </c>
+      <c r="F219" t="s">
+        <v>555</v>
+      </c>
+      <c r="G219">
+        <v>2025</v>
+      </c>
+      <c r="H219" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A220" s="8" t="s">
+        <v>740</v>
+      </c>
+      <c r="B220" s="8" t="s">
+        <v>830</v>
+      </c>
+      <c r="C220" s="9">
+        <v>50</v>
+      </c>
+      <c r="D220" t="s">
+        <v>551</v>
+      </c>
+      <c r="E220" t="s">
+        <v>821</v>
+      </c>
+      <c r="F220" t="s">
+        <v>555</v>
+      </c>
+      <c r="G220">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A221" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="B221" s="8" t="s">
+        <v>831</v>
+      </c>
+      <c r="C221" s="9">
+        <v>180</v>
+      </c>
+      <c r="D221" t="s">
+        <v>551</v>
+      </c>
+      <c r="E221" t="s">
+        <v>821</v>
+      </c>
+      <c r="F221" t="s">
+        <v>555</v>
+      </c>
+      <c r="G221">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A222" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="B222" s="8" t="s">
+        <v>832</v>
+      </c>
+      <c r="C222" s="9">
+        <v>530</v>
+      </c>
+      <c r="D222" t="s">
+        <v>551</v>
+      </c>
+      <c r="E222" t="s">
+        <v>824</v>
+      </c>
+      <c r="F222" t="s">
+        <v>555</v>
+      </c>
+      <c r="G222">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A223" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B223" s="8" t="s">
+        <v>833</v>
+      </c>
+      <c r="C223" s="9">
+        <v>600</v>
+      </c>
+      <c r="D223" t="s">
+        <v>551</v>
+      </c>
+      <c r="E223" t="s">
+        <v>826</v>
+      </c>
+      <c r="F223" t="s">
+        <v>555</v>
+      </c>
+      <c r="G223">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A224" s="8" t="s">
+        <v>734</v>
+      </c>
+      <c r="B224" s="8" t="s">
+        <v>833</v>
+      </c>
+      <c r="C224" s="9">
+        <v>1500</v>
+      </c>
+      <c r="D224" t="s">
+        <v>551</v>
+      </c>
+      <c r="E224" t="s">
+        <v>826</v>
+      </c>
+      <c r="F224" t="s">
+        <v>555</v>
+      </c>
+      <c r="G224">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A225" s="8" t="s">
+        <v>837</v>
+      </c>
+      <c r="B225" s="8" t="s">
+        <v>830</v>
+      </c>
+      <c r="C225" s="9">
+        <v>60</v>
+      </c>
+      <c r="D225" t="s">
+        <v>551</v>
+      </c>
+      <c r="E225" t="s">
+        <v>828</v>
+      </c>
+      <c r="F225" t="s">
+        <v>555</v>
+      </c>
+      <c r="G225">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A226" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="B226" s="8" t="s">
+        <v>834</v>
+      </c>
+      <c r="C226" s="9">
+        <v>120</v>
+      </c>
+      <c r="D226" t="s">
+        <v>551</v>
+      </c>
+      <c r="E226" t="s">
+        <v>828</v>
+      </c>
+      <c r="F226" t="s">
+        <v>555</v>
+      </c>
+      <c r="G226">
         <v>2025</v>
       </c>
     </row>
